--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G19">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G21">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G34">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU50"/>
+  <dimension ref="A1:AU49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-17 12:00:00</t>
+          <t>2026-09-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-17 12:30:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-17 13:00:00</t>
+          <t>2026-09-17 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-17 14:00:00</t>
+          <t>2026-09-17 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-17 14:30:00</t>
+          <t>2026-09-17 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-17 14:45:00</t>
+          <t>2026-09-17 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-17 15:00:00</t>
+          <t>2026-09-17 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-17 15:45:00</t>
+          <t>2026-09-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G45">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 16:30:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:00</t>
+          <t>2026-09-17 19:00:00</t>
         </is>
       </c>
     </row>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-17 19:00:00</t>
+          <t>2026-09-17 21:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,27 +8249,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G49">
@@ -8399,169 +8399,6 @@
         <v>0</v>
       </c>
       <c r="AU49" t="inlineStr">
-        <is>
-          <t>2026-09-17 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Bolívar</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Gualberto Villarroel SJ</t>
-        </is>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>0</v>
-      </c>
-      <c r="AK50">
-        <v>0</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>-1</v>
-      </c>
-      <c r="AQ50">
-        <v>0</v>
-      </c>
-      <c r="AR50">
-        <v>0</v>
-      </c>
-      <c r="AS50">
-        <v>0</v>
-      </c>
-      <c r="AT50">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-09-17 21:30:00</t>
         </is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AU48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G48">
@@ -8236,169 +8236,6 @@
         <v>0</v>
       </c>
       <c r="AU48" t="inlineStr">
-        <is>
-          <t>2026-09-17 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Bolívar</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Gualberto Villarroel SJ</t>
-        </is>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
-      <c r="AK49">
-        <v>0</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>-1</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
         <is>
           <t>2026-09-17 21:30:00</t>
         </is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G20">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G33">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL46">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G20">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G43">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -964,10 +964,10 @@
         <v>5.4</v>
       </c>
       <c r="O4">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q4">
         <v>5.45</v>
@@ -991,7 +991,7 @@
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
         <v>1.27</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>2.39</v>
       </c>
       <c r="AK4">
         <v>1.16</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1613,52 +1613,52 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="O8">
         <v>3.05</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q8">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="R8">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA8">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB8">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC8">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD8">
         <v>1.22</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G19">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G33">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G43">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -1133,55 +1133,55 @@
         <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G24">
@@ -4393,16 +4393,16 @@
         <v>9.75</v>
       </c>
       <c r="Q25">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="R25">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="S25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
         <v>1.56</v>
@@ -4420,19 +4420,19 @@
         <v>1.09</v>
       </c>
       <c r="Z25">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA25">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AB25">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC25">
         <v>1.45</v>
       </c>
       <c r="AD25">
-        <v>2.43</v>
+        <v>1.73</v>
       </c>
       <c r="AE25">
         <v>1.65</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK25">
-        <v>1.62</v>
+        <v>3.94</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -6020,19 +6020,19 @@
         <v>3.4</v>
       </c>
       <c r="P35">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S35">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T35">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="U35">
         <v>3.3</v>
@@ -6041,37 +6041,37 @@
         <v>1.29</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
         <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z35">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AA35">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AB35">
         <v>1.57</v>
       </c>
       <c r="AC35">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AD35">
         <v>1.17</v>
       </c>
       <c r="AE35">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF35">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AG35">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -967,58 +967,58 @@
         <v>4</v>
       </c>
       <c r="P4">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>5.45</v>
+        <v>5.13</v>
       </c>
       <c r="R4">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="U4">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="AA4">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AB4">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AC4">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AD4">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AG4">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AK4">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="O11">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="Q11">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="U11">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V11">
         <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
         <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.44</v>
+        <v>3.87</v>
       </c>
       <c r="AA11">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AB11">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AC11">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="AK11">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q12">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="V12">
         <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AB12">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC12">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="AD12">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>6.9</v>
       </c>
       <c r="Q22">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R22">
         <v>2.33</v>
@@ -3919,7 +3919,7 @@
         <v>2.59</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -6020,19 +6020,19 @@
         <v>3.4</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
       </c>
       <c r="R35">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S35">
         <v>1.51</v>
       </c>
       <c r="T35">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="U35">
         <v>3.3</v>
@@ -6053,25 +6053,25 @@
         <v>2.72</v>
       </c>
       <c r="AA35">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AB35">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC35">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="AD35">
         <v>1.17</v>
       </c>
       <c r="AE35">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AG35">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="O37">
         <v>3.34</v>
@@ -6349,55 +6349,55 @@
         <v>2.25</v>
       </c>
       <c r="Q37">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="R37">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S37">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T37">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U37">
+        <v>2.93</v>
+      </c>
+      <c r="V37">
+        <v>1.38</v>
+      </c>
+      <c r="W37">
+        <v>1.05</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.28</v>
+      </c>
+      <c r="Z37">
         <v>3.2</v>
       </c>
-      <c r="V37">
-        <v>1.33</v>
-      </c>
-      <c r="W37">
-        <v>1.03</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.36</v>
-      </c>
-      <c r="Z37">
-        <v>2.81</v>
-      </c>
       <c r="AA37">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="AB37">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC37">
-        <v>3.96</v>
+        <v>3.53</v>
       </c>
       <c r="AD37">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AG37">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AK37">
         <v>1.38</v>
@@ -6515,7 +6515,7 @@
         <v>8</v>
       </c>
       <c r="R38">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="S38">
         <v>1.2</v>
@@ -6530,22 +6530,22 @@
         <v>1.7</v>
       </c>
       <c r="W38">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y38">
         <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>5.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA38">
         <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AC38">
         <v>2.3</v>
@@ -6576,7 +6576,7 @@
         <v>4.2</v>
       </c>
       <c r="AK38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6992,28 +6992,28 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="O41">
         <v>3.5</v>
       </c>
       <c r="P41">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="Q41">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R41">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
         <v>2.89</v>
       </c>
       <c r="U41">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
         <v>1.42</v>
@@ -7025,28 +7025,28 @@
         <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z41">
         <v>3.38</v>
       </c>
       <c r="AA41">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC41">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AD41">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE41">
         <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG41">
         <v>2.09</v>
@@ -7065,7 +7065,7 @@
         <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7807,52 +7807,52 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O46">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q46">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="U46">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W46">
         <v>1.12</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z46">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA46">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB46">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC46">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AD46">
         <v>1.47</v>
@@ -7861,10 +7861,10 @@
         <v>1.15</v>
       </c>
       <c r="AF46">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
         <v>1.29</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU48"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G7">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8">
@@ -1609,68 +1609,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.16</v>
+        <v>3.11</v>
       </c>
       <c r="O8">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="P8">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-17 12:00:00</t>
+          <t>2026-09-17 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G9">
@@ -1772,68 +1772,68 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.24</v>
+        <v>4.62</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P11">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="Q11">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-17 12:30:00</t>
+          <t>2026-09-17 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="Q12">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="R12">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="U12">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.2</v>
+        <v>3.87</v>
       </c>
       <c r="AA12">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB12">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AC12">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG12">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK12">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-17 13:00:00</t>
+          <t>2026-09-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-17 14:00:00</t>
+          <t>2026-09-17 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-17 14:30:00</t>
+          <t>2026-09-17 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,81 +6340,81 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.18</v>
+        <v>1.8</v>
       </c>
       <c r="O37">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>2.25</v>
+        <v>4.94</v>
       </c>
       <c r="Q37">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="R37">
+        <v>2</v>
+      </c>
+      <c r="S37">
+        <v>1.51</v>
+      </c>
+      <c r="T37">
+        <v>2.39</v>
+      </c>
+      <c r="U37">
+        <v>3.3</v>
+      </c>
+      <c r="V37">
+        <v>1.29</v>
+      </c>
+      <c r="W37">
+        <v>1.02</v>
+      </c>
+      <c r="X37">
+        <v>1.05</v>
+      </c>
+      <c r="Y37">
+        <v>1.39</v>
+      </c>
+      <c r="Z37">
+        <v>2.72</v>
+      </c>
+      <c r="AA37">
+        <v>2.44</v>
+      </c>
+      <c r="AB37">
+        <v>1.66</v>
+      </c>
+      <c r="AC37">
+        <v>4.35</v>
+      </c>
+      <c r="AD37">
+        <v>1.17</v>
+      </c>
+      <c r="AE37">
+        <v>1.03</v>
+      </c>
+      <c r="AF37">
+        <v>2.11</v>
+      </c>
+      <c r="AG37">
+        <v>1.65</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>1.29</v>
+      </c>
+      <c r="AK37">
         <v>2.07</v>
       </c>
-      <c r="S37">
-        <v>1.43</v>
-      </c>
-      <c r="T37">
-        <v>2.77</v>
-      </c>
-      <c r="U37">
-        <v>2.93</v>
-      </c>
-      <c r="V37">
-        <v>1.38</v>
-      </c>
-      <c r="W37">
-        <v>1.05</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.28</v>
-      </c>
-      <c r="Z37">
-        <v>3.2</v>
-      </c>
-      <c r="AA37">
-        <v>2.01</v>
-      </c>
-      <c r="AB37">
-        <v>1.82</v>
-      </c>
-      <c r="AC37">
-        <v>3.53</v>
-      </c>
-      <c r="AD37">
-        <v>1.29</v>
-      </c>
-      <c r="AE37">
-        <v>1.05</v>
-      </c>
-      <c r="AF37">
-        <v>1.76</v>
-      </c>
-      <c r="AG37">
-        <v>1.95</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.65</v>
-      </c>
-      <c r="AK37">
-        <v>1.38</v>
-      </c>
       <c r="AL37">
         <v>0</v>
       </c>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-17 14:45:00</t>
+          <t>2026-09-17 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-17 15:00:00</t>
+          <t>2026-09-17 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-17 15:45:00</t>
+          <t>2026-09-17 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G40">
@@ -6825,68 +6825,68 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 15:45:00</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G45">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z46">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA46">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD46">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:00</t>
+          <t>2026-09-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-17 19:00:00</t>
+          <t>2026-09-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8086,156 +8086,482 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Málaga CF</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>3.55</v>
+      </c>
+      <c r="O48">
+        <v>3.75</v>
+      </c>
+      <c r="P48">
+        <v>2.01</v>
+      </c>
+      <c r="Q48">
+        <v>3.94</v>
+      </c>
+      <c r="R48">
+        <v>2.46</v>
+      </c>
+      <c r="S48">
+        <v>1.3</v>
+      </c>
+      <c r="T48">
+        <v>3.36</v>
+      </c>
+      <c r="U48">
+        <v>2.4</v>
+      </c>
+      <c r="V48">
+        <v>1.54</v>
+      </c>
+      <c r="W48">
+        <v>1.12</v>
+      </c>
+      <c r="X48">
+        <v>1.01</v>
+      </c>
+      <c r="Y48">
+        <v>1.21</v>
+      </c>
+      <c r="Z48">
+        <v>4.3</v>
+      </c>
+      <c r="AA48">
+        <v>1.65</v>
+      </c>
+      <c r="AB48">
+        <v>2.27</v>
+      </c>
+      <c r="AC48">
+        <v>2.46</v>
+      </c>
+      <c r="AD48">
+        <v>1.47</v>
+      </c>
+      <c r="AE48">
+        <v>1.15</v>
+      </c>
+      <c r="AF48">
+        <v>1.55</v>
+      </c>
+      <c r="AG48">
+        <v>2.32</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.2</v>
+      </c>
+      <c r="AK48">
+        <v>1.29</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-17 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Bolívar</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
-      </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
-      <c r="AG48">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
-      <c r="AN48">
-        <v>-1</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>-1</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-09-17 21:30:00</t>
         </is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>5.4</v>
+        <v>4.25</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
         <v>5.13</v>
@@ -994,10 +994,10 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="AA4">
         <v>1.87</v>
@@ -1034,7 +1034,7 @@
         <v>2.15</v>
       </c>
       <c r="AK4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="O6">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q6">
         <v>4.9</v>
@@ -1323,7 +1323,7 @@
         <v>1.37</v>
       </c>
       <c r="Z6">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AA6">
         <v>2.29</v>
@@ -2277,7 +2277,7 @@
         <v>3.8</v>
       </c>
       <c r="R12">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="S12">
         <v>1.33</v>
@@ -2292,7 +2292,7 @@
         <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2304,7 +2304,7 @@
         <v>3.87</v>
       </c>
       <c r="AA12">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
         <v>2.01</v>
@@ -2313,16 +2313,16 @@
         <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG12">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
         <v>1.37</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="R13">
         <v>2.22</v>
@@ -2464,7 +2464,7 @@
         <v>1.3</v>
       </c>
       <c r="Z13">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA13">
         <v>1.98</v>
@@ -2501,7 +2501,7 @@
         <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="P37">
-        <v>4.94</v>
+        <v>4.85</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -6355,7 +6355,7 @@
         <v>2</v>
       </c>
       <c r="S37">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T37">
         <v>2.39</v>
@@ -6364,10 +6364,10 @@
         <v>3.3</v>
       </c>
       <c r="V37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
         <v>1.05</v>
@@ -6379,19 +6379,19 @@
         <v>2.72</v>
       </c>
       <c r="AA37">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="AB37">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC37">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AD37">
         <v>1.17</v>
       </c>
       <c r="AE37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF37">
         <v>2.11</v>
@@ -6413,7 +6413,7 @@
         <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="O39">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q39">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="R39">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S39">
         <v>1.43</v>
       </c>
       <c r="T39">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="U39">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.3</v>
+      </c>
+      <c r="Z39">
+        <v>3.12</v>
+      </c>
+      <c r="AA39">
+        <v>2.06</v>
+      </c>
+      <c r="AB39">
+        <v>1.78</v>
+      </c>
+      <c r="AC39">
+        <v>3.65</v>
+      </c>
+      <c r="AD39">
         <v>1.28</v>
       </c>
-      <c r="Z39">
-        <v>3.2</v>
-      </c>
-      <c r="AA39">
-        <v>2.01</v>
-      </c>
-      <c r="AB39">
-        <v>1.82</v>
-      </c>
-      <c r="AC39">
-        <v>3.53</v>
-      </c>
-      <c r="AD39">
-        <v>1.29</v>
-      </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG39">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AK39">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q48">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="R48">
         <v>2.46</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T48">
         <v>3.36</v>
       </c>
       <c r="U48">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V48">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA48">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB48">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AC48">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AD48">
         <v>1.47</v>
       </c>
       <c r="AE48">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG48">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>3.87</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>5.13</v>
+        <v>4.95</v>
       </c>
       <c r="R4">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="S4">
         <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
         <v>2.54</v>
@@ -994,10 +994,10 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="AA4">
         <v>1.87</v>
@@ -1006,13 +1006,13 @@
         <v>2.08</v>
       </c>
       <c r="AC4">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AD4">
         <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF4">
         <v>1.74</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK4">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,22 +1296,22 @@
         <v>1.84</v>
       </c>
       <c r="Q6">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="R6">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S6">
         <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="U6">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="V6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W6">
         <v>1.02</v>
@@ -1360,7 +1360,7 @@
         <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
         <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="O9">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
         <v>2.8</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.62</v>
+        <v>4.4</v>
       </c>
       <c r="O11">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="P11">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>3.24</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P12">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q12">
         <v>3.8</v>
@@ -2307,7 +2307,7 @@
         <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AC12">
         <v>3</v>
@@ -2319,7 +2319,7 @@
         <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG12">
         <v>2.15</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q13">
-        <v>3.7</v>
+        <v>3.23</v>
       </c>
       <c r="R13">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
         <v>1.38</v>
@@ -2452,7 +2452,7 @@
         <v>2.92</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2473,7 +2473,7 @@
         <v>1.84</v>
       </c>
       <c r="AC13">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
         <v>1.31</v>
@@ -2482,10 +2482,10 @@
         <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3904,16 +3904,16 @@
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R22">
         <v>2.33</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
         <v>2.59</v>
@@ -3928,7 +3928,7 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
         <v>3.68</v>
@@ -3943,13 +3943,13 @@
         <v>2.83</v>
       </c>
       <c r="AD22">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
         <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG22">
         <v>1.76</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>8.15</v>
+        <v>7.7</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P36">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Q36">
         <v>7</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T36">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U36">
         <v>3.3</v>
       </c>
       <c r="V36">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X36">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z36">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AA36">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AB36">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC36">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD36">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF36">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AG36">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
         <v>1.08</v>
@@ -6343,19 +6343,19 @@
         <v>1.63</v>
       </c>
       <c r="O37">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S37">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T37">
         <v>2.39</v>
@@ -6364,28 +6364,28 @@
         <v>3.3</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X37">
         <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z37">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AA37">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB37">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC37">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD37">
         <v>1.17</v>
@@ -6394,10 +6394,10 @@
         <v>1.01</v>
       </c>
       <c r="AF37">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AG37">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
         <v>2.08</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P39">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="Q39">
-        <v>4</v>
+        <v>3.39</v>
       </c>
       <c r="R39">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="S39">
         <v>1.43</v>
@@ -6687,10 +6687,10 @@
         <v>2.72</v>
       </c>
       <c r="U39">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="V39">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
         <v>1.04</v>
@@ -6708,22 +6708,22 @@
         <v>2.06</v>
       </c>
       <c r="AB39">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC39">
         <v>3.65</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG39">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AK39">
         <v>1.36</v>
@@ -6871,7 +6871,7 @@
         <v>1.53</v>
       </c>
       <c r="AB40">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AC40">
         <v>2.3</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q43">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="U43">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V43">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
         <v>1.06</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AA43">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
         <v>1.88</v>
       </c>
       <c r="AC43">
-        <v>2.94</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE43">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
         <v>1.66</v>
       </c>
       <c r="AG43">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,25 +8136,25 @@
         <v>3.1</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="P48">
         <v>1.95</v>
       </c>
       <c r="Q48">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="R48">
         <v>2.46</v>
       </c>
       <c r="S48">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="U48">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
         <v>1.5</v>
@@ -8172,10 +8172,10 @@
         <v>3.8</v>
       </c>
       <c r="AA48">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB48">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AC48">
         <v>2.51</v>
@@ -8184,7 +8184,7 @@
         <v>1.47</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF48">
         <v>1.56</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="AK48">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="Q23">
         <v>2.54</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="O26">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="P26">
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R26">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="T26">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="U26">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="V26">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="W26">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z26">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="AA26">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AB26">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="AC26">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AD26">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AE26">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK26">
-        <v>3.94</v>
+        <v>4.15</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q29">
-        <v>2.82</v>
+        <v>3.24</v>
       </c>
       <c r="R29">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="T29">
-        <v>2.84</v>
+        <v>2.39</v>
       </c>
       <c r="U29">
-        <v>2.69</v>
+        <v>3.18</v>
       </c>
       <c r="V29">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X29">
+        <v>1.03</v>
+      </c>
+      <c r="Y29">
+        <v>1.36</v>
+      </c>
+      <c r="Z29">
+        <v>2.7</v>
+      </c>
+      <c r="AA29">
+        <v>2.2</v>
+      </c>
+      <c r="AB29">
+        <v>1.57</v>
+      </c>
+      <c r="AC29">
+        <v>4</v>
+      </c>
+      <c r="AD29">
+        <v>1.17</v>
+      </c>
+      <c r="AE29">
         <v>1.02</v>
       </c>
-      <c r="Y29">
-        <v>1.25</v>
-      </c>
-      <c r="Z29">
-        <v>3.28</v>
-      </c>
-      <c r="AA29">
-        <v>1.89</v>
-      </c>
-      <c r="AB29">
-        <v>1.78</v>
-      </c>
-      <c r="AC29">
-        <v>3.2</v>
-      </c>
-      <c r="AD29">
-        <v>1.26</v>
-      </c>
-      <c r="AE29">
-        <v>1.05</v>
-      </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG29">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.17</v>
+        <v>1.69</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
+        <v>2.4</v>
+      </c>
+      <c r="O31">
+        <v>3.1</v>
+      </c>
+      <c r="P31">
+        <v>2.62</v>
+      </c>
+      <c r="Q31">
+        <v>3.1</v>
+      </c>
+      <c r="R31">
+        <v>1.98</v>
+      </c>
+      <c r="S31">
+        <v>1.38</v>
+      </c>
+      <c r="T31">
         <v>2.65</v>
       </c>
-      <c r="O31">
-        <v>2.95</v>
-      </c>
-      <c r="P31">
-        <v>2.8</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="O34">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P34">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q34">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T34">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V34">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z34">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA34">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB34">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC34">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AD34">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG34">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O47">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P47">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q47">
         <v>4.04</v>
@@ -8009,10 +8009,10 @@
         <v>2.83</v>
       </c>
       <c r="AA47">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB47">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC47">
         <v>3.75</v>
@@ -8305,55 +8305,55 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -6340,28 +6340,28 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="O37">
         <v>3.4</v>
       </c>
       <c r="P37">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q37">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="R37">
         <v>1.99</v>
       </c>
       <c r="S37">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T37">
         <v>2.39</v>
       </c>
       <c r="U37">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V37">
         <v>1.29</v>
@@ -6370,22 +6370,22 @@
         <v>1.02</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y37">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z37">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AA37">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB37">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC37">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AD37">
         <v>1.17</v>
@@ -6394,10 +6394,10 @@
         <v>1.01</v>
       </c>
       <c r="AF37">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AG37">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -8145,16 +8145,16 @@
         <v>4.1</v>
       </c>
       <c r="R48">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="S48">
         <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
         <v>1.5</v>
@@ -8172,13 +8172,13 @@
         <v>3.8</v>
       </c>
       <c r="AA48">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB48">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AC48">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AD48">
         <v>1.47</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,10 +8305,10 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S49">
         <v>1.22</v>
@@ -8347,7 +8347,7 @@
         <v>1.56</v>
       </c>
       <c r="AE49">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF49">
         <v>1.44</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK49">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8471,7 +8471,7 @@
         <v>1.33</v>
       </c>
       <c r="R50">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="S50">
         <v>1.09</v>
@@ -8480,10 +8480,10 @@
         <v>6.1</v>
       </c>
       <c r="U50">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V50">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W50">
         <v>1.39</v>
@@ -8501,7 +8501,7 @@
         <v>1.13</v>
       </c>
       <c r="AB50">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AC50">
         <v>1.4</v>
@@ -8510,13 +8510,13 @@
         <v>2.56</v>
       </c>
       <c r="AE50">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AG50">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -810,7 +810,7 @@
         <v>2.65</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
         <v>1.3</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.15</v>
+        <v>4.68</v>
       </c>
       <c r="O4">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="P4">
         <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>4.95</v>
+        <v>4.18</v>
       </c>
       <c r="R4">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
         <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U4">
         <v>2.54</v>
@@ -1000,16 +1000,16 @@
         <v>3.68</v>
       </c>
       <c r="AA4">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB4">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AC4">
         <v>2.9</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE4">
         <v>1.09</v>
@@ -1018,7 +1018,7 @@
         <v>1.74</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,43 +1124,43 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O5">
         <v>2.75</v>
       </c>
       <c r="P5">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q5">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R5">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="S5">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T5">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U5">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y5">
         <v>1.62</v>
       </c>
       <c r="Z5">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AA5">
         <v>2.88</v>
@@ -1169,10 +1169,10 @@
         <v>1.4</v>
       </c>
       <c r="AC5">
-        <v>5.65</v>
+        <v>5.3</v>
       </c>
       <c r="AD5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE5">
         <v>1.03</v>
@@ -1181,7 +1181,7 @@
         <v>2.3</v>
       </c>
       <c r="AG5">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK5">
         <v>1.67</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O6">
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>4.7</v>
+        <v>4.95</v>
       </c>
       <c r="R6">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S6">
         <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="U6">
         <v>3.18</v>
@@ -1323,7 +1323,7 @@
         <v>1.37</v>
       </c>
       <c r="Z6">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="AA6">
         <v>2.29</v>
@@ -1344,7 +1344,7 @@
         <v>2.03</v>
       </c>
       <c r="AG6">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AK6">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
         <v>2.2</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,49 +1785,49 @@
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U9">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA9">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AB9">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD9">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
         <v>1.67</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.4</v>
+        <v>5.92</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="P11">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="R11">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U11">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2141,13 +2141,13 @@
         <v>3.3</v>
       </c>
       <c r="AA11">
+        <v>1.87</v>
+      </c>
+      <c r="AB11">
         <v>1.9</v>
       </c>
-      <c r="AB11">
-        <v>1.86</v>
-      </c>
       <c r="AC11">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD11">
         <v>1.3</v>
@@ -2156,10 +2156,10 @@
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG11">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK11">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="O12">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P12">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q12">
         <v>3.8</v>
@@ -2280,16 +2280,16 @@
         <v>2.31</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
         <v>1.09</v>
@@ -2301,25 +2301,25 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.87</v>
+        <v>3.66</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AD12">
         <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AG12">
         <v>2.15</v>
@@ -2338,7 +2338,7 @@
         <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
         <v>3.23</v>
@@ -2446,13 +2446,13 @@
         <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="U13">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2464,19 +2464,19 @@
         <v>1.3</v>
       </c>
       <c r="Z13">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="AA13">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AB13">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC13">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE13">
         <v>1.11</v>
@@ -2485,7 +2485,7 @@
         <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
         <v>1.34</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O22">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="Q22">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R22">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="S22">
         <v>1.33</v>
       </c>
       <c r="T22">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U22">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB22">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AC22">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD22">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
         <v>1.97</v>
       </c>
       <c r="AG22">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK22">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O23">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P23">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>2.54</v>
+        <v>1.99</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T23">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U23">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
         <v>1.05</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z23">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA23">
         <v>1.93</v>
       </c>
       <c r="AB23">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD23">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AG23">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>1.77</v>
+        <v>2.52</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R26">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="S26">
         <v>1.12</v>
@@ -4583,28 +4583,28 @@
         <v>1.03</v>
       </c>
       <c r="Z26">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AA26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB26">
         <v>4.1</v>
       </c>
       <c r="AC26">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AD26">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE26">
         <v>1.47</v>
       </c>
       <c r="AF26">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG26">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK26">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5042,7 +5042,7 @@
         <v>2.9</v>
       </c>
       <c r="P29">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Q29">
         <v>3.24</v>
@@ -5075,7 +5075,7 @@
         <v>2.7</v>
       </c>
       <c r="AA29">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB29">
         <v>1.57</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P31">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
       </c>
       <c r="R31">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U31">
         <v>2.77</v>
@@ -5404,7 +5404,7 @@
         <v>2.1</v>
       </c>
       <c r="AB31">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC31">
         <v>3.5</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O32">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P32">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q32">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S32">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T32">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="U32">
         <v>3.06</v>
@@ -5570,13 +5570,13 @@
         <v>1.55</v>
       </c>
       <c r="AC32">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD32">
         <v>1.16</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF32">
         <v>1.9</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
         <v>1.47</v>
@@ -5697,22 +5697,22 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
         <v>1.04</v>
@@ -5730,7 +5730,7 @@
         <v>2.05</v>
       </c>
       <c r="AB33">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
         <v>3.58</v>
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="R34">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S34">
         <v>1.45</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="U34">
         <v>3</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
         <v>1.53</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="O36">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
         <v>1.48</v>
@@ -6198,13 +6198,13 @@
         <v>2.34</v>
       </c>
       <c r="U36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V36">
         <v>1.25</v>
       </c>
       <c r="W36">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
         <v>1.03</v>
@@ -6213,28 +6213,28 @@
         <v>1.38</v>
       </c>
       <c r="Z36">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA36">
         <v>2.38</v>
       </c>
       <c r="AB36">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC36">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD36">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE36">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AG36">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="Q37">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R37">
         <v>1.99</v>
       </c>
       <c r="S37">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T37">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="U37">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="V37">
         <v>1.29</v>
       </c>
       <c r="W37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y37">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z37">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AA37">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB37">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC37">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE37">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG37">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O39">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="Q39">
-        <v>3.39</v>
+        <v>4.02</v>
       </c>
       <c r="R39">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="S39">
         <v>1.43</v>
       </c>
       <c r="T39">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="U39">
         <v>3.02</v>
@@ -6708,10 +6708,10 @@
         <v>2.06</v>
       </c>
       <c r="AB39">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC39">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="AD39">
         <v>1.25</v>
@@ -6720,10 +6720,10 @@
         <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG39">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
         <v>1.36</v>
@@ -6871,7 +6871,7 @@
         <v>1.53</v>
       </c>
       <c r="AB40">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC40">
         <v>2.3</v>
@@ -7318,58 +7318,58 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P43">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q43">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="R43">
         <v>2.13</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>3.08</v>
+        <v>2.73</v>
       </c>
       <c r="U43">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V43">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA43">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC43">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD43">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
         <v>1.66</v>
@@ -7391,7 +7391,7 @@
         <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>2.8</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="O45">
         <v>3.85</v>
       </c>
       <c r="P45">
-        <v>6.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7976,58 +7976,58 @@
         <v>3</v>
       </c>
       <c r="P47">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q47">
-        <v>4.04</v>
+        <v>3.75</v>
       </c>
       <c r="R47">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T47">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="U47">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="V47">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W47">
+        <v>1.01</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.37</v>
+      </c>
+      <c r="Z47">
+        <v>2.66</v>
+      </c>
+      <c r="AA47">
+        <v>2.22</v>
+      </c>
+      <c r="AB47">
+        <v>1.56</v>
+      </c>
+      <c r="AC47">
+        <v>4.1</v>
+      </c>
+      <c r="AD47">
+        <v>1.16</v>
+      </c>
+      <c r="AE47">
         <v>1.02</v>
       </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.33</v>
-      </c>
-      <c r="Z47">
-        <v>2.83</v>
-      </c>
-      <c r="AA47">
-        <v>2.2</v>
-      </c>
-      <c r="AB47">
-        <v>1.65</v>
-      </c>
-      <c r="AC47">
-        <v>3.75</v>
-      </c>
-      <c r="AD47">
-        <v>1.19</v>
-      </c>
-      <c r="AE47">
-        <v>1.03</v>
-      </c>
       <c r="AF47">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG47">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="AK47">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8139,46 +8139,46 @@
         <v>3.63</v>
       </c>
       <c r="P48">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q48">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
         <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
         <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB48">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="AC48">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AD48">
         <v>1.47</v>
@@ -8187,10 +8187,10 @@
         <v>1.15</v>
       </c>
       <c r="AF48">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8305,25 +8305,25 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="R49">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U49">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V49">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8335,16 +8335,16 @@
         <v>4.75</v>
       </c>
       <c r="AA49">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB49">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC49">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AD49">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE49">
         <v>1.21</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8474,16 +8474,16 @@
         <v>3.12</v>
       </c>
       <c r="S50">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T50">
         <v>6.1</v>
       </c>
       <c r="U50">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V50">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="W50">
         <v>1.39</v>
@@ -8498,25 +8498,25 @@
         <v>11</v>
       </c>
       <c r="AA50">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AB50">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AC50">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AD50">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AE50">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AF50">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -1130,7 +1130,7 @@
         <v>2.75</v>
       </c>
       <c r="P5">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q5">
         <v>2.62</v>
@@ -1139,10 +1139,10 @@
         <v>1.85</v>
       </c>
       <c r="S5">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T5">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U5">
         <v>3.82</v>
@@ -1157,16 +1157,16 @@
         <v>1.14</v>
       </c>
       <c r="Y5">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z5">
         <v>2.28</v>
       </c>
       <c r="AA5">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB5">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC5">
         <v>5.3</v>
@@ -1815,10 +1815,10 @@
         <v>3.28</v>
       </c>
       <c r="AA9">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AC9">
         <v>3.14</v>
@@ -1833,7 +1833,7 @@
         <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -6177,28 +6177,28 @@
         </is>
       </c>
       <c r="N36">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P36">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q36">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S36">
         <v>1.48</v>
       </c>
       <c r="T36">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="U36">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V36">
         <v>1.25</v>
@@ -6210,25 +6210,25 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z36">
         <v>2.88</v>
       </c>
       <c r="AA36">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AB36">
         <v>1.55</v>
       </c>
       <c r="AC36">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD36">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE36">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF36">
         <v>2.55</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U3">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC3">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AG3">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-09-17 10:00:00</t>
+          <t>2026-09-17 10:15:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.68</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>3.86</v>
+        <v>2.75</v>
       </c>
       <c r="P4">
-        <v>1.61</v>
+        <v>4.28</v>
       </c>
       <c r="Q4">
-        <v>4.18</v>
+        <v>2.81</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="T4">
-        <v>3.18</v>
+        <v>2.05</v>
       </c>
       <c r="U4">
-        <v>2.54</v>
+        <v>3.82</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
+        <v>1.01</v>
+      </c>
+      <c r="X4">
         <v>1.1</v>
       </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="Z4">
-        <v>3.68</v>
+        <v>2.18</v>
       </c>
       <c r="AA4">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB4">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AC4">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD4">
+        <v>1.09</v>
+      </c>
+      <c r="AE4">
+        <v>1.03</v>
+      </c>
+      <c r="AF4">
+        <v>2.25</v>
+      </c>
+      <c r="AG4">
+        <v>1.53</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.34</v>
       </c>
-      <c r="AE4">
-        <v>1.09</v>
-      </c>
-      <c r="AF4">
-        <v>1.74</v>
-      </c>
-      <c r="AG4">
-        <v>1.98</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.29</v>
-      </c>
       <c r="AK4">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-17 10:15:00</t>
+          <t>2026-09-17 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.05</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q5">
-        <v>2.62</v>
+        <v>4.95</v>
       </c>
       <c r="R5">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="U5">
-        <v>3.82</v>
+        <v>3.18</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
+        <v>1.02</v>
+      </c>
+      <c r="X5">
         <v>1.03</v>
       </c>
-      <c r="X5">
-        <v>1.14</v>
-      </c>
       <c r="Y5">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="Z5">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="AA5">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AB5">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AC5">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AD5">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AG5">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.7</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="Q6">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
+        <v>2.21</v>
+      </c>
+      <c r="O7">
+        <v>3.4</v>
+      </c>
+      <c r="P7">
+        <v>3.12</v>
+      </c>
+      <c r="Q7">
+        <v>2.65</v>
+      </c>
+      <c r="R7">
+        <v>2.3</v>
+      </c>
+      <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
+        <v>3.1</v>
+      </c>
+      <c r="U7">
+        <v>2.55</v>
+      </c>
+      <c r="V7">
+        <v>1.45</v>
+      </c>
+      <c r="W7">
+        <v>1.09</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.22</v>
+      </c>
+      <c r="Z7">
+        <v>3.8</v>
+      </c>
+      <c r="AA7">
+        <v>1.81</v>
+      </c>
+      <c r="AB7">
+        <v>1.96</v>
+      </c>
+      <c r="AC7">
+        <v>2.8</v>
+      </c>
+      <c r="AD7">
+        <v>1.38</v>
+      </c>
+      <c r="AE7">
+        <v>1.11</v>
+      </c>
+      <c r="AF7">
         <v>1.66</v>
       </c>
-      <c r="O7">
-        <v>3.55</v>
-      </c>
-      <c r="P7">
-        <v>4.4</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="P8">
         <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
         <v>1.32</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.34</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
         <v>3.1</v>
@@ -1815,10 +1815,10 @@
         <v>3.28</v>
       </c>
       <c r="AA9">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB9">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC9">
         <v>3.14</v>
@@ -1830,7 +1830,7 @@
         <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
         <v>1.99</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.92</v>
+        <v>8.1</v>
       </c>
       <c r="O11">
         <v>4.01</v>
       </c>
       <c r="P11">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q11">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S11">
         <v>1.37</v>
@@ -2129,37 +2129,37 @@
         <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
         <v>1.87</v>
       </c>
       <c r="AB11">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC11">
         <v>3.1</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE11">
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG11">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="O12">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="P12">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="R12">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
         <v>3.08</v>
@@ -2298,22 +2298,22 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
         <v>1.09</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q13">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T13">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U13">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="V13">
         <v>1.38</v>
@@ -2467,19 +2467,19 @@
         <v>3.41</v>
       </c>
       <c r="AA13">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AB13">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AC13">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
         <v>1.27</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
         <v>1.75</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="O22">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="P22">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="Q22">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R22">
         <v>2.28</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T22">
-        <v>2.95</v>
+        <v>3.09</v>
       </c>
       <c r="U22">
         <v>2.63</v>
@@ -3934,16 +3934,16 @@
         <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC22">
         <v>2.92</v>
       </c>
       <c r="AD22">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE22">
         <v>1.08</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AK22">
         <v>2.68</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O23">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="Q23">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="R23">
         <v>2.22</v>
@@ -4079,10 +4079,10 @@
         <v>2.78</v>
       </c>
       <c r="U23">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W23">
         <v>1.05</v>
@@ -4091,19 +4091,19 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z23">
         <v>3.2</v>
       </c>
       <c r="AA23">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC23">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AD23">
         <v>1.32</v>
@@ -5042,7 +5042,7 @@
         <v>2.9</v>
       </c>
       <c r="P29">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q29">
         <v>3.24</v>
@@ -5075,7 +5075,7 @@
         <v>2.7</v>
       </c>
       <c r="AA29">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
         <v>1.57</v>
@@ -5208,55 +5208,55 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U31">
         <v>2.77</v>
@@ -5401,7 +5401,7 @@
         <v>2.92</v>
       </c>
       <c r="AA31">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB31">
         <v>1.68</v>
@@ -5416,10 +5416,10 @@
         <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG31">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q32">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S32">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T32">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="U32">
         <v>3.06</v>
@@ -5558,31 +5558,31 @@
         <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z32">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA32">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AB32">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC32">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AD32">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE32">
         <v>1.01</v>
       </c>
       <c r="AF32">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG32">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK32">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q33">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R33">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
         <v>1.04</v>
@@ -5721,31 +5721,31 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG33">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O34">
         <v>3.1</v>
       </c>
       <c r="P34">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q34">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="R34">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="S34">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T34">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z34">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA34">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AB34">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC34">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD34">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE34">
         <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG34">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O36">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="P36">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q36">
         <v>8.25</v>
@@ -6195,7 +6195,7 @@
         <v>1.48</v>
       </c>
       <c r="T36">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="U36">
         <v>3.3</v>
@@ -6210,31 +6210,31 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z36">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA36">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AB36">
         <v>1.55</v>
       </c>
       <c r="AC36">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD36">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE36">
         <v>1.01</v>
       </c>
       <c r="AF36">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AG36">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P37">
-        <v>4.75</v>
+        <v>5.45</v>
       </c>
       <c r="Q37">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="R37">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T37">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U37">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="V37">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
         <v>1.03</v>
       </c>
       <c r="X37">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z37">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA37">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB37">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC37">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AD37">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AG37">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,22 +6666,22 @@
         </is>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P39">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q39">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="R39">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="S39">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T39">
         <v>2.7</v>
@@ -6705,7 +6705,7 @@
         <v>3.12</v>
       </c>
       <c r="AA39">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AB39">
         <v>1.84</v>
@@ -6723,7 +6723,7 @@
         <v>1.79</v>
       </c>
       <c r="AG39">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>1.53</v>
       </c>
       <c r="AB40">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AC40">
         <v>2.3</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7046,10 +7046,10 @@
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="O43">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q43">
         <v>3.54</v>
@@ -7336,46 +7336,46 @@
         <v>1.35</v>
       </c>
       <c r="T43">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="U43">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V43">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z43">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA43">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB43">
         <v>1.9</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD43">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE43">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF43">
         <v>1.66</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
         <v>1.39</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O44">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q44">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R44">
         <v>1.9</v>
@@ -7526,7 +7526,7 @@
         <v>1.63</v>
       </c>
       <c r="AC44">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AD44">
         <v>1.19</v>
@@ -7554,7 +7554,7 @@
         <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,25 +7647,25 @@
         <v>1.48</v>
       </c>
       <c r="O45">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P45">
         <v>5.75</v>
       </c>
       <c r="Q45">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R45">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S45">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T45">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U45">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="V45">
         <v>1.33</v>
@@ -7677,28 +7677,28 @@
         <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z45">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="AA45">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB45">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC45">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AD45">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE45">
         <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AG45">
         <v>1.56</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
         <v>2.27</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,55 +7979,55 @@
         <v>2.2</v>
       </c>
       <c r="Q47">
-        <v>3.75</v>
+        <v>4.16</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S47">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T47">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U47">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="V47">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W47">
         <v>1.01</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z47">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA47">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AB47">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC47">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD47">
         <v>1.16</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG47">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8139,46 +8139,46 @@
         <v>3.63</v>
       </c>
       <c r="P48">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="R48">
         <v>2.29</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U48">
         <v>2.4</v>
       </c>
       <c r="V48">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y48">
         <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA48">
         <v>1.7</v>
       </c>
       <c r="AB48">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="AC48">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="AD48">
         <v>1.47</v>
@@ -8190,7 +8190,7 @@
         <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -1785,55 +1785,55 @@
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="R9">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U9">
-        <v>2.61</v>
+        <v>2.89</v>
       </c>
       <c r="V9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
         <v>1.25</v>
       </c>
       <c r="Z9">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD9">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE9">
         <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O26">
         <v>6.5</v>
       </c>
       <c r="P26">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q26">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R26">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="S26">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T26">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="U26">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="W26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.03</v>
       </c>
       <c r="Z26">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AA26">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AB26">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AC26">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AD26">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE26">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AF26">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK26">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="O37">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="Q37">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R37">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S37">
         <v>1.46</v>
@@ -6394,7 +6394,7 @@
         <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AG37">
         <v>1.68</v>
@@ -6413,7 +6413,7 @@
         <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O41">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA41">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AB41">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG41">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O48">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="P48">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q48">
         <v>4.05</v>
       </c>
       <c r="R48">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>1.32</v>
@@ -8157,13 +8157,13 @@
         <v>2.4</v>
       </c>
       <c r="V48">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
         <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.17</v>
@@ -8175,7 +8175,7 @@
         <v>1.7</v>
       </c>
       <c r="AB48">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AC48">
         <v>2.46</v>
@@ -8184,13 +8184,13 @@
         <v>1.47</v>
       </c>
       <c r="AE48">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,25 +8305,25 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T49">
         <v>3.7</v>
       </c>
       <c r="U49">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V49">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8332,13 +8332,13 @@
         <v>1.12</v>
       </c>
       <c r="Z49">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA49">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC49">
         <v>2.2</v>
@@ -8350,10 +8350,10 @@
         <v>1.21</v>
       </c>
       <c r="AF49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,22 +8468,22 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R50">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
       <c r="S50">
         <v>1.08</v>
       </c>
       <c r="T50">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="U50">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="V50">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="W50">
         <v>1.39</v>
@@ -8495,28 +8495,28 @@
         <v>1.03</v>
       </c>
       <c r="Z50">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AA50">
         <v>1.12</v>
       </c>
       <c r="AB50">
-        <v>4.65</v>
+        <v>6</v>
       </c>
       <c r="AC50">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AD50">
-        <v>2.59</v>
+        <v>2.92</v>
       </c>
       <c r="AE50">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AG50">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK50">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="R49">
         <v>2.34</v>
@@ -8323,7 +8323,7 @@
         <v>1.59</v>
       </c>
       <c r="W49">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8335,10 +8335,10 @@
         <v>4.8</v>
       </c>
       <c r="AA49">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AB49">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC49">
         <v>2.2</v>
@@ -8350,10 +8350,10 @@
         <v>1.21</v>
       </c>
       <c r="AF49">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG49">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="R50">
         <v>3.48</v>
@@ -8480,28 +8480,28 @@
         <v>7.5</v>
       </c>
       <c r="U50">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V50">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="W50">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X50">
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z50">
         <v>13.5</v>
       </c>
       <c r="AA50">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AB50">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AC50">
         <v>1.31</v>
@@ -8510,13 +8510,13 @@
         <v>2.92</v>
       </c>
       <c r="AE50">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AF50">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AG50">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.03</v>
       </c>
       <c r="AK50">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -5042,58 +5042,58 @@
         <v>2.9</v>
       </c>
       <c r="P29">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q29">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R29">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S29">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T29">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U29">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="V29">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z29">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AA29">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC29">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE29">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG29">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK29">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,61 +5202,61 @@
         <v>1.69</v>
       </c>
       <c r="O30">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.61</v>
+        <v>2.86</v>
       </c>
       <c r="U30">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y30">
+        <v>1.23</v>
+      </c>
+      <c r="Z30">
+        <v>3.42</v>
+      </c>
+      <c r="AA30">
+        <v>1.8</v>
+      </c>
+      <c r="AB30">
+        <v>1.87</v>
+      </c>
+      <c r="AC30">
+        <v>3.3</v>
+      </c>
+      <c r="AD30">
         <v>1.3</v>
       </c>
-      <c r="Z30">
-        <v>2.97</v>
-      </c>
-      <c r="AA30">
-        <v>2.02</v>
-      </c>
-      <c r="AB30">
-        <v>1.68</v>
-      </c>
-      <c r="AC30">
-        <v>3.5</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK30">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
       </c>
       <c r="R31">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T31">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U31">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="V31">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z31">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AA31">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AB31">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC31">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG31">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK31">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>2.9</v>
       </c>
       <c r="Q32">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="R32">
         <v>1.89</v>
@@ -5543,46 +5543,46 @@
         <v>1.45</v>
       </c>
       <c r="T32">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="U32">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="V32">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z32">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="AA32">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AB32">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC32">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD32">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.28</v>
       </c>
       <c r="AK32">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q33">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="R33">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="U33">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V33">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
+        <v>1.05</v>
+      </c>
+      <c r="Y33">
+        <v>1.37</v>
+      </c>
+      <c r="Z33">
+        <v>2.66</v>
+      </c>
+      <c r="AA33">
+        <v>2.18</v>
+      </c>
+      <c r="AB33">
+        <v>1.57</v>
+      </c>
+      <c r="AC33">
+        <v>4.4</v>
+      </c>
+      <c r="AD33">
+        <v>1.18</v>
+      </c>
+      <c r="AE33">
         <v>1.01</v>
       </c>
-      <c r="Y33">
-        <v>1.32</v>
-      </c>
-      <c r="Z33">
-        <v>2.88</v>
-      </c>
-      <c r="AA33">
-        <v>2.08</v>
-      </c>
-      <c r="AB33">
-        <v>1.64</v>
-      </c>
-      <c r="AC33">
-        <v>3.78</v>
-      </c>
-      <c r="AD33">
-        <v>1.19</v>
-      </c>
-      <c r="AE33">
-        <v>1.02</v>
-      </c>
       <c r="AF33">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG33">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK33">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
+        <v>2.75</v>
+      </c>
+      <c r="P34">
+        <v>2.65</v>
+      </c>
+      <c r="Q34">
+        <v>3.5</v>
+      </c>
+      <c r="R34">
+        <v>1.91</v>
+      </c>
+      <c r="S34">
+        <v>1.49</v>
+      </c>
+      <c r="T34">
+        <v>2.44</v>
+      </c>
+      <c r="U34">
         <v>3.1</v>
       </c>
-      <c r="P34">
-        <v>3</v>
-      </c>
-      <c r="Q34">
-        <v>3.08</v>
-      </c>
-      <c r="R34">
-        <v>1.88</v>
-      </c>
-      <c r="S34">
-        <v>1.44</v>
-      </c>
-      <c r="T34">
-        <v>2.45</v>
-      </c>
-      <c r="U34">
-        <v>3.06</v>
-      </c>
       <c r="V34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W34">
         <v>1.02</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z34">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AA34">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="AB34">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC34">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD34">
         <v>1.15</v>
       </c>
       <c r="AE34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG34">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7484,61 +7484,61 @@
         <v>2.45</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P44">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q44">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="R44">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
         <v>1.44</v>
       </c>
       <c r="T44">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U44">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="V44">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z44">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="AA44">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB44">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC44">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD44">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE44">
         <v>1.02</v>
       </c>
       <c r="AF44">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="O45">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P45">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="Q45">
+        <v>2.26</v>
+      </c>
+      <c r="R45">
         <v>2.12</v>
       </c>
-      <c r="R45">
-        <v>1.95</v>
-      </c>
       <c r="S45">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T45">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="U45">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V45">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W45">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y45">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z45">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA45">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB45">
         <v>1.61</v>
       </c>
       <c r="AC45">
-        <v>3.74</v>
+        <v>4.4</v>
       </c>
       <c r="AD45">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE45">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AG45">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AK45">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,61 +7807,61 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="O46">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q46">
-        <v>3.14</v>
+        <v>3.71</v>
       </c>
       <c r="R46">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="S46">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="T46">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="U46">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="V46">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z46">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="AA46">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AB46">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC46">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD46">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE46">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AG46">
         <v>1.91</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK46">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O47">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P47">
         <v>2.2</v>
       </c>
       <c r="Q47">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="R47">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S47">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T47">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U47">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="V47">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z47">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA47">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AB47">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC47">
-        <v>4.15</v>
+        <v>3.84</v>
       </c>
       <c r="AD47">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG47">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -801,28 +801,28 @@
         <v>4.2</v>
       </c>
       <c r="O3">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="R3">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="U3">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="V3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
         <v>1.1</v>
@@ -837,10 +837,10 @@
         <v>3.68</v>
       </c>
       <c r="AA3">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC3">
         <v>2.85</v>
@@ -849,13 +849,13 @@
         <v>1.35</v>
       </c>
       <c r="AE3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
         <v>1.22</v>
@@ -967,28 +967,28 @@
         <v>2.75</v>
       </c>
       <c r="P4">
-        <v>4.28</v>
+        <v>3.9</v>
       </c>
       <c r="Q4">
         <v>2.81</v>
       </c>
       <c r="R4">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S4">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="T4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
         <v>3.82</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
         <v>1.1</v>
@@ -1015,10 +1015,10 @@
         <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG4">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.34</v>
       </c>
       <c r="AK4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
         <v>4.95</v>
@@ -1139,10 +1139,10 @@
         <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T5">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U5">
         <v>3.18</v>
@@ -1157,13 +1157,13 @@
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z5">
         <v>2.66</v>
       </c>
       <c r="AA5">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AB5">
         <v>1.64</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="O7">
         <v>3.4</v>
       </c>
       <c r="P7">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="Q7">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U7">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="V7">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA7">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AB7">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AG7">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O8">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="Q8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z8">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA8">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AK8">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>8.1</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="P11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q11">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="R11">
         <v>2.27</v>
       </c>
       <c r="S11">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U11">
         <v>2.85</v>
@@ -2129,37 +2129,37 @@
         <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA11">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB11">
         <v>1.86</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD11">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG11">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="O12">
         <v>3.47</v>
@@ -2274,16 +2274,16 @@
         <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U12">
         <v>2.57</v>
@@ -2304,25 +2304,25 @@
         <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC12">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="AD12">
         <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
         <v>1.64</v>
       </c>
       <c r="AG12">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="O13">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="Q13">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S13">
         <v>1.43</v>
@@ -2449,10 +2449,10 @@
         <v>2.73</v>
       </c>
       <c r="U13">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2461,31 +2461,31 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z13">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="AA13">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AB13">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD13">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG13">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AK13">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="O22">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="P22">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="Q22">
         <v>1.94</v>
@@ -3910,10 +3910,10 @@
         <v>2.28</v>
       </c>
       <c r="S22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="U22">
         <v>2.63</v>
@@ -3931,10 +3931,10 @@
         <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB22">
         <v>1.96</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O23">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="P23">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>2.01</v>
@@ -4079,10 +4079,10 @@
         <v>2.78</v>
       </c>
       <c r="U23">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="V23">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
         <v>1.05</v>
@@ -4097,16 +4097,16 @@
         <v>3.2</v>
       </c>
       <c r="AA23">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB23">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC23">
         <v>3.14</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE23">
         <v>1.07</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,34 +6180,34 @@
         <v>7.6</v>
       </c>
       <c r="O36">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q36">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="R36">
         <v>1.97</v>
       </c>
       <c r="S36">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T36">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V36">
         <v>1.25</v>
       </c>
       <c r="W36">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
         <v>1.38</v>
@@ -6216,19 +6216,19 @@
         <v>2.62</v>
       </c>
       <c r="AA36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB36">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC36">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD36">
         <v>1.15</v>
       </c>
       <c r="AE36">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
         <v>2.4</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="AK36">
         <v>1.02</v>
@@ -6349,7 +6349,7 @@
         <v>5.4</v>
       </c>
       <c r="Q37">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="R37">
         <v>1.98</v>
@@ -6382,7 +6382,7 @@
         <v>2.2</v>
       </c>
       <c r="AB37">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC37">
         <v>4</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O38">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="P38">
         <v>8.5</v>
       </c>
       <c r="Q38">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R38">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T38">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="U38">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="V38">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z38">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA38">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AB38">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AC38">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF38">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AG38">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK38">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,10 +6669,10 @@
         <v>2.85</v>
       </c>
       <c r="O39">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P39">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="Q39">
         <v>3.95</v>
@@ -6699,7 +6699,7 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z39">
         <v>3.12</v>
@@ -6711,10 +6711,10 @@
         <v>1.84</v>
       </c>
       <c r="AC39">
-        <v>3.44</v>
+        <v>3.65</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
         <v>1.05</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6871,7 +6871,7 @@
         <v>1.53</v>
       </c>
       <c r="AB40">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC40">
         <v>2.3</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O41">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="R41">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="S41">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T41">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="U41">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="V41">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z41">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="AA41">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB41">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AC41">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="AD41">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG41">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,37 +7155,37 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O42">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P42">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q42">
-        <v>3.46</v>
+        <v>4.17</v>
       </c>
       <c r="R42">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="S42">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="T42">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="U42">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="V42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W42">
         <v>1.03</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
         <v>1.49</v>
@@ -7194,25 +7194,25 @@
         <v>2.38</v>
       </c>
       <c r="AA42">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AB42">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AC42">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AD42">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AG42">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK42">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q43">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="R43">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
         <v>1.35</v>
@@ -7345,37 +7345,37 @@
         <v>1.41</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA43">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC43">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AD43">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
         <v>1.09</v>
       </c>
       <c r="AF43">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AG43">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O44">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>2.81</v>
+        <v>3.71</v>
       </c>
       <c r="R44">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="S44">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T44">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U44">
         <v>2.9</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X44">
         <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="AA44">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AB44">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC44">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE44">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG44">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="O45">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="P45">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q45">
-        <v>2.26</v>
+        <v>2.81</v>
       </c>
       <c r="R45">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S45">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T45">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="U45">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V45">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
         <v>1.05</v>
@@ -7680,28 +7680,28 @@
         <v>1.36</v>
       </c>
       <c r="Z45">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="AA45">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB45">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC45">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD45">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE45">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="O46">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="Q46">
-        <v>3.71</v>
+        <v>2.26</v>
       </c>
       <c r="R46">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="S46">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T46">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="U46">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V46">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W46">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
         <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z46">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="AA46">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AB46">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC46">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD46">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE46">
+        <v>1.04</v>
+      </c>
+      <c r="AF46">
+        <v>2.13</v>
+      </c>
+      <c r="AG46">
+        <v>1.62</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.07</v>
       </c>
-      <c r="AF46">
-        <v>1.82</v>
-      </c>
-      <c r="AG46">
-        <v>1.91</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.28</v>
-      </c>
       <c r="AK46">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,16 +8142,16 @@
         <v>1.91</v>
       </c>
       <c r="Q48">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R48">
         <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U48">
         <v>2.4</v>
@@ -8160,7 +8160,7 @@
         <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8169,16 +8169,16 @@
         <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA48">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB48">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AC48">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AD48">
         <v>1.47</v>
@@ -8305,13 +8305,13 @@
         <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="R49">
         <v>2.34</v>
       </c>
       <c r="S49">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
         <v>3.7</v>
@@ -8320,10 +8320,10 @@
         <v>2.17</v>
       </c>
       <c r="V49">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8338,22 +8338,22 @@
         <v>1.46</v>
       </c>
       <c r="AB49">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AC49">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD49">
         <v>1.57</v>
       </c>
       <c r="AE49">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q50">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="R50">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="S50">
         <v>1.08</v>
@@ -8480,10 +8480,10 @@
         <v>7.5</v>
       </c>
       <c r="U50">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V50">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="W50">
         <v>1.38</v>
@@ -8492,16 +8492,16 @@
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z50">
         <v>13.5</v>
       </c>
       <c r="AA50">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB50">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AC50">
         <v>1.31</v>
@@ -8513,10 +8513,10 @@
         <v>1.93</v>
       </c>
       <c r="AF50">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.03</v>
       </c>
       <c r="AK50">
-        <v>6.55</v>
+        <v>6.3</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -1830,7 +1830,7 @@
         <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG9">
         <v>1.86</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q14">
-        <v>2.3</v>
+        <v>3.57</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S14">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="U14">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="AA14">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AB14">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.83</v>
+        <v>1.8</v>
       </c>
       <c r="O15">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T15">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="U15">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.04</v>
@@ -2793,25 +2793,25 @@
         <v>3.34</v>
       </c>
       <c r="AA15">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB15">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC15">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P16">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q16">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="R16">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
         <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA16">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC16">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="AD16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="O17">
+        <v>3.38</v>
+      </c>
+      <c r="P17">
+        <v>2.28</v>
+      </c>
+      <c r="Q17">
         <v>3.4</v>
       </c>
-      <c r="P17">
-        <v>1.91</v>
-      </c>
-      <c r="Q17">
-        <v>4.22</v>
-      </c>
       <c r="R17">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="AA17">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AB17">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="O18">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q18">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
         <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z18">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB18">
+        <v>2.07</v>
+      </c>
+      <c r="AC18">
+        <v>2.59</v>
+      </c>
+      <c r="AD18">
+        <v>1.39</v>
+      </c>
+      <c r="AE18">
+        <v>1.12</v>
+      </c>
+      <c r="AF18">
+        <v>1.74</v>
+      </c>
+      <c r="AG18">
+        <v>1.94</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.11</v>
+      </c>
+      <c r="AK18">
         <v>2.25</v>
-      </c>
-      <c r="AC18">
-        <v>2.68</v>
-      </c>
-      <c r="AD18">
-        <v>1.4</v>
-      </c>
-      <c r="AE18">
-        <v>1.13</v>
-      </c>
-      <c r="AF18">
-        <v>1.6</v>
-      </c>
-      <c r="AG18">
-        <v>2.15</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.2</v>
-      </c>
-      <c r="AK18">
-        <v>1.81</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="O19">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>5.44</v>
+        <v>1.91</v>
       </c>
       <c r="Q19">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z19">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AA19">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB19">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AC19">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE19">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>2.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="P20">
-        <v>3.1</v>
+        <v>5.44</v>
       </c>
       <c r="Q20">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="R20">
+        <v>2.38</v>
+      </c>
+      <c r="S20">
+        <v>1.29</v>
+      </c>
+      <c r="T20">
+        <v>3.12</v>
+      </c>
+      <c r="U20">
+        <v>2.5</v>
+      </c>
+      <c r="V20">
+        <v>1.5</v>
+      </c>
+      <c r="W20">
+        <v>1.13</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.2</v>
+      </c>
+      <c r="Z20">
+        <v>4.1</v>
+      </c>
+      <c r="AA20">
+        <v>1.61</v>
+      </c>
+      <c r="AB20">
+        <v>2.25</v>
+      </c>
+      <c r="AC20">
+        <v>2.42</v>
+      </c>
+      <c r="AD20">
+        <v>1.44</v>
+      </c>
+      <c r="AE20">
+        <v>1.15</v>
+      </c>
+      <c r="AF20">
+        <v>1.61</v>
+      </c>
+      <c r="AG20">
         <v>2.09</v>
       </c>
-      <c r="S20">
-        <v>1.32</v>
-      </c>
-      <c r="T20">
-        <v>2.89</v>
-      </c>
-      <c r="U20">
-        <v>2.57</v>
-      </c>
-      <c r="V20">
-        <v>1.4</v>
-      </c>
-      <c r="W20">
-        <v>1.1</v>
-      </c>
-      <c r="X20">
-        <v>1.04</v>
-      </c>
-      <c r="Y20">
-        <v>1.19</v>
-      </c>
-      <c r="Z20">
-        <v>4.2</v>
-      </c>
-      <c r="AA20">
-        <v>1.74</v>
-      </c>
-      <c r="AB20">
-        <v>1.94</v>
-      </c>
-      <c r="AC20">
-        <v>2.83</v>
-      </c>
-      <c r="AD20">
-        <v>1.33</v>
-      </c>
-      <c r="AE20">
-        <v>1.09</v>
-      </c>
-      <c r="AF20">
-        <v>1.62</v>
-      </c>
-      <c r="AG20">
-        <v>2.12</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="O21">
         <v>3.3</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q21">
-        <v>3.57</v>
+        <v>2.57</v>
       </c>
       <c r="R21">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T21">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="U21">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="V21">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
         <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z21">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AA21">
+        <v>1.74</v>
+      </c>
+      <c r="AB21">
+        <v>1.94</v>
+      </c>
+      <c r="AC21">
+        <v>2.83</v>
+      </c>
+      <c r="AD21">
+        <v>1.33</v>
+      </c>
+      <c r="AE21">
+        <v>1.09</v>
+      </c>
+      <c r="AF21">
+        <v>1.62</v>
+      </c>
+      <c r="AG21">
+        <v>2.12</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.22</v>
+      </c>
+      <c r="AK21">
         <v>1.66</v>
-      </c>
-      <c r="AB21">
-        <v>2.15</v>
-      </c>
-      <c r="AC21">
-        <v>2.68</v>
-      </c>
-      <c r="AD21">
-        <v>1.43</v>
-      </c>
-      <c r="AE21">
-        <v>1.12</v>
-      </c>
-      <c r="AF21">
-        <v>1.57</v>
-      </c>
-      <c r="AG21">
-        <v>2.26</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.23</v>
-      </c>
-      <c r="AK21">
-        <v>1.32</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O26">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q26">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R26">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="S26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T26">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V26">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="W26">
         <v>1.25</v>
@@ -4580,31 +4580,31 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z26">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="AA26">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB26">
         <v>3.34</v>
       </c>
       <c r="AC26">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD26">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AE26">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.05</v>
       </c>
       <c r="AK26">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -6023,25 +6023,25 @@
         <v>2</v>
       </c>
       <c r="Q35">
-        <v>5.14</v>
+        <v>4.8</v>
       </c>
       <c r="R35">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S35">
         <v>1.54</v>
       </c>
       <c r="T35">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="U35">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="V35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
         <v>1.06</v>
@@ -6059,19 +6059,19 @@
         <v>1.44</v>
       </c>
       <c r="AC35">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD35">
         <v>1.11</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF35">
         <v>2.17</v>
       </c>
       <c r="AG35">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7164,16 +7164,16 @@
         <v>2.48</v>
       </c>
       <c r="Q42">
-        <v>4.17</v>
+        <v>3.75</v>
       </c>
       <c r="R42">
         <v>1.82</v>
       </c>
       <c r="S42">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T42">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="U42">
         <v>3.58</v>
@@ -7182,7 +7182,7 @@
         <v>1.21</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
         <v>1.05</v>
@@ -7206,13 +7206,13 @@
         <v>1.1</v>
       </c>
       <c r="AE42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF42">
         <v>2.09</v>
       </c>
       <c r="AG42">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G15">
@@ -2757,77 +2757,77 @@
         <v>1.8</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
         <v>3.75</v>
       </c>
       <c r="Q15">
+        <v>2.33</v>
+      </c>
+      <c r="R15">
         <v>2.3</v>
       </c>
-      <c r="R15">
-        <v>2.2</v>
-      </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="U15">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AB15">
+        <v>2.25</v>
+      </c>
+      <c r="AC15">
+        <v>2.68</v>
+      </c>
+      <c r="AD15">
+        <v>1.4</v>
+      </c>
+      <c r="AE15">
+        <v>1.13</v>
+      </c>
+      <c r="AF15">
+        <v>1.6</v>
+      </c>
+      <c r="AG15">
+        <v>2.15</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.2</v>
+      </c>
+      <c r="AK15">
         <v>1.81</v>
-      </c>
-      <c r="AC15">
-        <v>3.25</v>
-      </c>
-      <c r="AD15">
-        <v>1.33</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
-      <c r="AF15">
-        <v>1.73</v>
-      </c>
-      <c r="AG15">
-        <v>2</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.21</v>
-      </c>
-      <c r="AK15">
-        <v>1.86</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G16">
@@ -2920,61 +2920,61 @@
         <v>1.8</v>
       </c>
       <c r="O16">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
         <v>3.75</v>
       </c>
       <c r="Q16">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>3.9</v>
+        <v>3.34</v>
       </c>
       <c r="AA16">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AB16">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC16">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>4.22</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U17">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="AA17">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AB17">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC17">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,37 +3243,37 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q18">
-        <v>2.04</v>
+        <v>2.57</v>
       </c>
       <c r="R18">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U18">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.19</v>
@@ -3282,25 +3282,25 @@
         <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB18">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AC18">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD18">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF18">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="O19">
+        <v>3.38</v>
+      </c>
+      <c r="P19">
+        <v>2.28</v>
+      </c>
+      <c r="Q19">
         <v>3.4</v>
       </c>
-      <c r="P19">
-        <v>1.91</v>
-      </c>
-      <c r="Q19">
-        <v>4.22</v>
-      </c>
       <c r="R19">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="AD19">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK19">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>5.44</v>
+        <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R20">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB20">
+        <v>2.07</v>
+      </c>
+      <c r="AC20">
+        <v>2.59</v>
+      </c>
+      <c r="AD20">
+        <v>1.39</v>
+      </c>
+      <c r="AE20">
+        <v>1.12</v>
+      </c>
+      <c r="AF20">
+        <v>1.74</v>
+      </c>
+      <c r="AG20">
+        <v>1.94</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.11</v>
+      </c>
+      <c r="AK20">
         <v>2.25</v>
-      </c>
-      <c r="AC20">
-        <v>2.42</v>
-      </c>
-      <c r="AD20">
-        <v>1.44</v>
-      </c>
-      <c r="AE20">
-        <v>1.15</v>
-      </c>
-      <c r="AF20">
-        <v>1.61</v>
-      </c>
-      <c r="AG20">
-        <v>2.09</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.17</v>
-      </c>
-      <c r="AK20">
-        <v>2.2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="P21">
-        <v>3.1</v>
+        <v>5.44</v>
       </c>
       <c r="Q21">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="R21">
+        <v>2.38</v>
+      </c>
+      <c r="S21">
+        <v>1.29</v>
+      </c>
+      <c r="T21">
+        <v>3.12</v>
+      </c>
+      <c r="U21">
+        <v>2.5</v>
+      </c>
+      <c r="V21">
+        <v>1.5</v>
+      </c>
+      <c r="W21">
+        <v>1.13</v>
+      </c>
+      <c r="X21">
+        <v>1.01</v>
+      </c>
+      <c r="Y21">
+        <v>1.2</v>
+      </c>
+      <c r="Z21">
+        <v>4.1</v>
+      </c>
+      <c r="AA21">
+        <v>1.61</v>
+      </c>
+      <c r="AB21">
+        <v>2.25</v>
+      </c>
+      <c r="AC21">
+        <v>2.42</v>
+      </c>
+      <c r="AD21">
+        <v>1.44</v>
+      </c>
+      <c r="AE21">
+        <v>1.15</v>
+      </c>
+      <c r="AF21">
+        <v>1.61</v>
+      </c>
+      <c r="AG21">
         <v>2.09</v>
       </c>
-      <c r="S21">
-        <v>1.32</v>
-      </c>
-      <c r="T21">
-        <v>2.89</v>
-      </c>
-      <c r="U21">
-        <v>2.57</v>
-      </c>
-      <c r="V21">
-        <v>1.4</v>
-      </c>
-      <c r="W21">
-        <v>1.1</v>
-      </c>
-      <c r="X21">
-        <v>1.04</v>
-      </c>
-      <c r="Y21">
-        <v>1.19</v>
-      </c>
-      <c r="Z21">
-        <v>4.2</v>
-      </c>
-      <c r="AA21">
-        <v>1.74</v>
-      </c>
-      <c r="AB21">
-        <v>1.94</v>
-      </c>
-      <c r="AC21">
-        <v>2.83</v>
-      </c>
-      <c r="AD21">
-        <v>1.33</v>
-      </c>
-      <c r="AE21">
-        <v>1.09</v>
-      </c>
-      <c r="AF21">
-        <v>1.62</v>
-      </c>
-      <c r="AG21">
-        <v>2.12</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -970,7 +970,7 @@
         <v>3.9</v>
       </c>
       <c r="Q4">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="R4">
         <v>1.75</v>
@@ -979,13 +979,13 @@
         <v>1.57</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U4">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
         <v>1.02</v>
@@ -994,10 +994,10 @@
         <v>1.1</v>
       </c>
       <c r="Y4">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z4">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AA4">
         <v>2.7</v>
@@ -1012,7 +1012,7 @@
         <v>1.09</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
         <v>2.32</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>4.95</v>
+        <v>5.16</v>
       </c>
       <c r="R5">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U5">
         <v>3.18</v>
@@ -1157,7 +1157,7 @@
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z5">
         <v>2.66</v>
@@ -1166,7 +1166,7 @@
         <v>2.28</v>
       </c>
       <c r="AB5">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC5">
         <v>4</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>4.5</v>
+        <v>3.32</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O12">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q12">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="R12">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="U12">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AB12">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>3.01</v>
+        <v>3.24</v>
       </c>
       <c r="AD12">
+        <v>1.31</v>
+      </c>
+      <c r="AE12">
+        <v>1.11</v>
+      </c>
+      <c r="AF12">
+        <v>1.74</v>
+      </c>
+      <c r="AG12">
+        <v>2</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.52</v>
+      </c>
+      <c r="AK12">
         <v>1.34</v>
-      </c>
-      <c r="AE12">
-        <v>1.14</v>
-      </c>
-      <c r="AF12">
-        <v>1.64</v>
-      </c>
-      <c r="AG12">
-        <v>2.12</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.22</v>
-      </c>
-      <c r="AK12">
-        <v>1.38</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="O13">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="P13">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="R13">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="S13">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>2.73</v>
+        <v>3.18</v>
       </c>
       <c r="U13">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z13">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AC13">
-        <v>3.24</v>
+        <v>3.01</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P14">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q14">
-        <v>3.57</v>
+        <v>2.33</v>
       </c>
       <c r="R14">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
         <v>1.28</v>
@@ -2612,43 +2612,43 @@
         <v>3.12</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AA14">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB14">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
         <v>2.68</v>
       </c>
       <c r="AD14">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG14">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G15">
@@ -2757,61 +2757,61 @@
         <v>1.8</v>
       </c>
       <c r="O15">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
         <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T15">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z15">
-        <v>3.9</v>
+        <v>3.34</v>
       </c>
       <c r="AA15">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AB15">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC15">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>4.22</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
+        <v>1.3</v>
+      </c>
+      <c r="T16">
+        <v>2.99</v>
+      </c>
+      <c r="U16">
+        <v>2.45</v>
+      </c>
+      <c r="V16">
+        <v>1.44</v>
+      </c>
+      <c r="W16">
+        <v>1.09</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1.19</v>
+      </c>
+      <c r="Z16">
+        <v>3.78</v>
+      </c>
+      <c r="AA16">
+        <v>1.69</v>
+      </c>
+      <c r="AB16">
+        <v>2.01</v>
+      </c>
+      <c r="AC16">
+        <v>2.66</v>
+      </c>
+      <c r="AD16">
         <v>1.37</v>
       </c>
-      <c r="T16">
-        <v>2.86</v>
-      </c>
-      <c r="U16">
-        <v>2.65</v>
-      </c>
-      <c r="V16">
-        <v>1.38</v>
-      </c>
-      <c r="W16">
-        <v>1.06</v>
-      </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
-      <c r="Y16">
-        <v>1.24</v>
-      </c>
-      <c r="Z16">
-        <v>3.34</v>
-      </c>
-      <c r="AA16">
-        <v>1.86</v>
-      </c>
-      <c r="AB16">
-        <v>1.81</v>
-      </c>
-      <c r="AC16">
-        <v>3.25</v>
-      </c>
-      <c r="AD16">
-        <v>1.33</v>
-      </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>1.86</v>
+        <v>1.21</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
-        <v>4.22</v>
+        <v>2.57</v>
       </c>
       <c r="R17">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T17">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AB17">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
         <v>3.3</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
-        <v>2.57</v>
+        <v>3.57</v>
       </c>
       <c r="R18">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="U18">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W18">
         <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA18">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AB18">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC18">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AD18">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE18">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3904,16 +3904,16 @@
         <v>6.9</v>
       </c>
       <c r="Q22">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R22">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
         <v>1.33</v>
       </c>
       <c r="T22">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="U22">
         <v>2.63</v>
@@ -3922,7 +3922,7 @@
         <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -3931,13 +3931,13 @@
         <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC22">
         <v>2.92</v>
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AG22">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>6</v>
       </c>
       <c r="Q23">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="R23">
         <v>2.22</v>
@@ -4079,10 +4079,10 @@
         <v>2.78</v>
       </c>
       <c r="U23">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W23">
         <v>1.05</v>
@@ -4097,10 +4097,10 @@
         <v>3.2</v>
       </c>
       <c r="AA23">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB23">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC23">
         <v>3.14</v>
@@ -4131,7 +4131,7 @@
         <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O27">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O29">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q29">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="S29">
         <v>1.47</v>
       </c>
       <c r="T29">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U29">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="V29">
         <v>1.28</v>
@@ -5069,31 +5069,31 @@
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AA29">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC29">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="AD29">
         <v>1.2</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
         <v>1.82</v>
       </c>
       <c r="AG29">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,49 +5199,49 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="O30">
         <v>3.6</v>
       </c>
       <c r="P30">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Q30">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V30">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB30">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC30">
         <v>3.3</v>
@@ -5250,13 +5250,13 @@
         <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK30">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,22 +5365,22 @@
         <v>2.5</v>
       </c>
       <c r="O31">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S31">
         <v>1.43</v>
       </c>
       <c r="T31">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U31">
         <v>2.86</v>
@@ -5404,22 +5404,22 @@
         <v>2.15</v>
       </c>
       <c r="AB31">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC31">
         <v>3.58</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
         <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG31">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,37 +5525,37 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
         <v>3</v>
       </c>
       <c r="P32">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q32">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S32">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T32">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="U32">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="V32">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
         <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.35</v>
@@ -5564,25 +5564,25 @@
         <v>2.74</v>
       </c>
       <c r="AA32">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB32">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC32">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD32">
         <v>1.18</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG32">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.28</v>
       </c>
       <c r="AK32">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P33">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q33">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R33">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="S33">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T33">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U33">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V33">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y33">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z33">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AB33">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
         <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,52 +5851,52 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P34">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="Q34">
         <v>3.5</v>
       </c>
       <c r="R34">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S34">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T34">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U34">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z34">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="AA34">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AB34">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC34">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD34">
         <v>1.15</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="O36">
         <v>3.6</v>
@@ -6195,10 +6195,10 @@
         <v>1.5</v>
       </c>
       <c r="T36">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="U36">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V36">
         <v>1.25</v>
@@ -6216,7 +6216,7 @@
         <v>2.62</v>
       </c>
       <c r="AA36">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AB36">
         <v>1.54</v>
@@ -6225,16 +6225,16 @@
         <v>4.25</v>
       </c>
       <c r="AD36">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE36">
         <v>1.05</v>
       </c>
       <c r="AF36">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AG36">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7481,25 +7481,25 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q44">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="R44">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S44">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T44">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U44">
         <v>2.9</v>
@@ -7508,22 +7508,22 @@
         <v>1.35</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X44">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="AA44">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB44">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC44">
         <v>4.1</v>
@@ -7535,7 +7535,7 @@
         <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG44">
         <v>1.91</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7659,16 +7659,16 @@
         <v>2.05</v>
       </c>
       <c r="S45">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="U45">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V45">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W45">
         <v>1.06</v>
@@ -7680,16 +7680,16 @@
         <v>1.36</v>
       </c>
       <c r="Z45">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AA45">
         <v>2.13</v>
       </c>
       <c r="AB45">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC45">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AD45">
         <v>1.2</v>
@@ -7698,10 +7698,10 @@
         <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG45">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK45">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q46">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="R46">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T46">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="U46">
         <v>3.2</v>
       </c>
       <c r="V46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W46">
+        <v>1.02</v>
+      </c>
+      <c r="X46">
         <v>1.03</v>
       </c>
-      <c r="X46">
-        <v>1.05</v>
-      </c>
       <c r="Y46">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z46">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AA46">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB46">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC46">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="AD46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE46">
         <v>1.04</v>
       </c>
       <c r="AF46">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AG46">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK46">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="O47">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P47">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q47">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="R47">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S47">
         <v>1.46</v>
@@ -7991,10 +7991,10 @@
         <v>2.39</v>
       </c>
       <c r="U47">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="V47">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
         <v>1.04</v>
@@ -8009,13 +8009,13 @@
         <v>2.74</v>
       </c>
       <c r="AA47">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB47">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC47">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AD47">
         <v>1.18</v>
@@ -8024,10 +8024,10 @@
         <v>1.06</v>
       </c>
       <c r="AF47">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG47">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AK47">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="R3">
         <v>2.27</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
         <v>3.05</v>
@@ -831,25 +831,25 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z3">
-        <v>3.68</v>
+        <v>3.91</v>
       </c>
       <c r="AA3">
         <v>1.7</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC3">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="AD3">
         <v>1.35</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
         <v>1.73</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>3.9</v>
       </c>
       <c r="Q4">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R4">
         <v>1.75</v>
@@ -994,7 +994,7 @@
         <v>1.1</v>
       </c>
       <c r="Y4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z4">
         <v>2.17</v>
@@ -1018,7 +1018,7 @@
         <v>2.32</v>
       </c>
       <c r="AG4">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>5.16</v>
+        <v>5.25</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S5">
         <v>1.44</v>
@@ -1163,10 +1163,10 @@
         <v>2.66</v>
       </c>
       <c r="AA5">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AB5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC5">
         <v>4</v>
@@ -1296,28 +1296,28 @@
         <v>3.32</v>
       </c>
       <c r="Q6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
         <v>3</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
         <v>1.27</v>
@@ -1326,10 +1326,10 @@
         <v>3.3</v>
       </c>
       <c r="AA6">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
         <v>3.2</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,61 +1453,61 @@
         <v>2.12</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="Q7">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="S7">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA7">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE7">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,61 +1616,61 @@
         <v>2.62</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>2.31</v>
+        <v>2.51</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
         <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="AA8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB8">
         <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="AD8">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG8">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O9">
         <v>3.3</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q9">
         <v>2.63</v>
@@ -1791,19 +1791,19 @@
         <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="U9">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="V9">
         <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.06</v>
@@ -1815,7 +1815,7 @@
         <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB9">
         <v>1.81</v>
@@ -1830,7 +1830,7 @@
         <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
         <v>1.86</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="O11">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="Q11">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
       <c r="R11">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB11">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AG11">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,61 +2268,61 @@
         <v>2.95</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P12">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q12">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="R12">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="AA12">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AB12">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AC12">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="AD12">
         <v>1.31</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2437,55 +2437,55 @@
         <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="R13">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="U13">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z13">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="AA13">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB13">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AC13">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="AD13">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="O14">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q14">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="AA14">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AB14">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AC14">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q15">
+        <v>4</v>
+      </c>
+      <c r="R15">
         <v>2.3</v>
       </c>
-      <c r="R15">
-        <v>2.2</v>
-      </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="AC15">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="AD15">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,61 +2917,61 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P16">
-        <v>1.91</v>
+        <v>3.55</v>
       </c>
       <c r="Q16">
-        <v>4.22</v>
+        <v>2.38</v>
       </c>
       <c r="R16">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V16">
+        <v>1.5</v>
+      </c>
+      <c r="W16">
+        <v>1.1</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.18</v>
+      </c>
+      <c r="Z16">
+        <v>3.86</v>
+      </c>
+      <c r="AA16">
+        <v>1.66</v>
+      </c>
+      <c r="AB16">
+        <v>2.05</v>
+      </c>
+      <c r="AC16">
+        <v>2.59</v>
+      </c>
+      <c r="AD16">
         <v>1.44</v>
       </c>
-      <c r="W16">
-        <v>1.09</v>
-      </c>
-      <c r="X16">
-        <v>1</v>
-      </c>
-      <c r="Y16">
-        <v>1.19</v>
-      </c>
-      <c r="Z16">
-        <v>3.78</v>
-      </c>
-      <c r="AA16">
-        <v>1.69</v>
-      </c>
-      <c r="AB16">
-        <v>2.01</v>
-      </c>
-      <c r="AC16">
-        <v>2.66</v>
-      </c>
-      <c r="AD16">
-        <v>1.37</v>
-      </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
         <v>2.15</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,22 +3083,22 @@
         <v>2</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
         <v>3.1</v>
       </c>
       <c r="Q17">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R17">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S17">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U17">
         <v>2.57</v>
@@ -3107,37 +3107,37 @@
         <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
         <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB17">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC17">
         <v>2.83</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,49 +3252,49 @@
         <v>2.2</v>
       </c>
       <c r="Q18">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="R18">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
         <v>3.12</v>
       </c>
       <c r="U18">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="V18">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AA18">
         <v>1.66</v>
       </c>
       <c r="AB18">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AC18">
         <v>2.68</v>
       </c>
       <c r="AD18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
         <v>1.57</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AK18">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -3421,10 +3421,10 @@
         <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U19">
         <v>2.58</v>
@@ -3445,10 +3445,10 @@
         <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB19">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC19">
         <v>3.05</v>
@@ -3457,13 +3457,13 @@
         <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
         <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="S20">
         <v>1.3</v>
@@ -3590,43 +3590,43 @@
         <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA20">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB20">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC20">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD20">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AG20">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.11</v>
       </c>
       <c r="AK20">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O21">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>5.44</v>
+        <v>4</v>
       </c>
       <c r="Q21">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R21">
+        <v>2.4</v>
+      </c>
+      <c r="S21">
+        <v>1.28</v>
+      </c>
+      <c r="T21">
+        <v>3.3</v>
+      </c>
+      <c r="U21">
         <v>2.38</v>
       </c>
-      <c r="S21">
-        <v>1.29</v>
-      </c>
-      <c r="T21">
-        <v>3.12</v>
-      </c>
-      <c r="U21">
-        <v>2.5</v>
-      </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W21">
         <v>1.13</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
+        <v>1.16</v>
+      </c>
+      <c r="Z21">
+        <v>4.5</v>
+      </c>
+      <c r="AA21">
+        <v>1.65</v>
+      </c>
+      <c r="AB21">
+        <v>2.2</v>
+      </c>
+      <c r="AC21">
+        <v>2.41</v>
+      </c>
+      <c r="AD21">
+        <v>1.45</v>
+      </c>
+      <c r="AE21">
         <v>1.2</v>
       </c>
-      <c r="Z21">
-        <v>4.1</v>
-      </c>
-      <c r="AA21">
-        <v>1.61</v>
-      </c>
-      <c r="AB21">
-        <v>2.25</v>
-      </c>
-      <c r="AC21">
-        <v>2.42</v>
-      </c>
-      <c r="AD21">
-        <v>1.44</v>
-      </c>
-      <c r="AE21">
-        <v>1.15</v>
-      </c>
       <c r="AF21">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG21">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>4.45</v>
       </c>
       <c r="P22">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="Q22">
         <v>1.91</v>
@@ -4131,7 +4131,7 @@
         <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O24">
         <v>8</v>
       </c>
       <c r="P24">
-        <v>9.609999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4396,13 +4396,13 @@
         <v>1.91</v>
       </c>
       <c r="R25">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U25">
         <v>2.2</v>
@@ -4411,13 +4411,13 @@
         <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
         <v>4.6</v>
@@ -4432,10 +4432,10 @@
         <v>2.28</v>
       </c>
       <c r="AD25">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE25">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF25">
         <v>1.57</v>
@@ -4457,7 +4457,7 @@
         <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O26">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="P26">
         <v>9.75</v>
       </c>
       <c r="Q26">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R26">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="S26">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T26">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="U26">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V26">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="W26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z26">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB26">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AC26">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD26">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE26">
         <v>1.44</v>
       </c>
       <c r="AF26">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK26">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O35">
         <v>2.9</v>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q35">
         <v>4.8</v>
@@ -6029,7 +6029,7 @@
         <v>1.95</v>
       </c>
       <c r="S35">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="T35">
         <v>2.27</v>
@@ -6044,7 +6044,7 @@
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y35">
         <v>1.5</v>
@@ -6059,16 +6059,16 @@
         <v>1.44</v>
       </c>
       <c r="AC35">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD35">
         <v>1.11</v>
       </c>
       <c r="AE35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF35">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AG35">
         <v>1.62</v>
@@ -6195,7 +6195,7 @@
         <v>1.5</v>
       </c>
       <c r="T36">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="U36">
         <v>3.3</v>
@@ -6228,7 +6228,7 @@
         <v>1.21</v>
       </c>
       <c r="AE36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
         <v>2.42</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
         <v>5.4</v>
       </c>
       <c r="Q37">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R37">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="S37">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T37">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U37">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="V37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W37">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AA37">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB37">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC37">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD37">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG37">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O38">
         <v>4.1</v>
       </c>
       <c r="P38">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R38">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="U38">
         <v>2.86</v>
       </c>
       <c r="V38">
+        <v>1.35</v>
+      </c>
+      <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
         <v>1.33</v>
       </c>
-      <c r="W38">
-        <v>1.04</v>
-      </c>
-      <c r="X38">
-        <v>1.04</v>
-      </c>
-      <c r="Y38">
-        <v>1.37</v>
-      </c>
       <c r="Z38">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA38">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB38">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC38">
         <v>4.1</v>
       </c>
       <c r="AD38">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE38">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AG38">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AK38">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="O39">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P39">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="Q39">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="R39">
         <v>2.06</v>
@@ -6699,19 +6699,19 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="AA39">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB39">
         <v>1.84</v>
       </c>
       <c r="AC39">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="AD39">
         <v>1.28</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,40 +6829,40 @@
         </is>
       </c>
       <c r="N40">
-        <v>11.2</v>
+        <v>6</v>
       </c>
       <c r="O40">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="Q40">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="R40">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U40">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="V40">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z40">
         <v>4.5</v>
@@ -6877,7 +6877,7 @@
         <v>2.3</v>
       </c>
       <c r="AD40">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AE40">
         <v>1.22</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="AK40">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6998,58 +6998,58 @@
         <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="R41">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S41">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="U41">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V41">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z41">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="AA41">
         <v>2.01</v>
       </c>
       <c r="AB41">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC41">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="AD41">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE41">
         <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG41">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.36</v>
       </c>
       <c r="AK41">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>3.05</v>
       </c>
       <c r="O42">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P42">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -7173,13 +7173,13 @@
         <v>1.57</v>
       </c>
       <c r="T42">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="U42">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="V42">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W42">
         <v>1.04</v>
@@ -7194,7 +7194,7 @@
         <v>2.38</v>
       </c>
       <c r="AA42">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AB42">
         <v>1.5</v>
@@ -7209,10 +7209,10 @@
         <v>1.02</v>
       </c>
       <c r="AF42">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AG42">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>1.35</v>
       </c>
       <c r="T43">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="U43">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="V43">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
         <v>1.1</v>
@@ -7351,31 +7351,31 @@
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA43">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC43">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AD43">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE43">
         <v>1.09</v>
       </c>
       <c r="AF43">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>1.91</v>
       </c>
       <c r="Q48">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
         <v>2.3</v>
@@ -8151,7 +8151,7 @@
         <v>1.31</v>
       </c>
       <c r="T48">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U48">
         <v>2.4</v>
@@ -8160,25 +8160,25 @@
         <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z48">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB48">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AC48">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AD48">
         <v>1.47</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="AK48">
         <v>1.29</v>
@@ -8305,10 +8305,10 @@
         <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="R49">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8317,43 +8317,43 @@
         <v>3.7</v>
       </c>
       <c r="U49">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="V49">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z49">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="AA49">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB49">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AC49">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AD49">
         <v>1.57</v>
       </c>
       <c r="AE49">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>14.5</v>
       </c>
       <c r="Q50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R50">
         <v>3.34</v>
@@ -8483,25 +8483,25 @@
         <v>1.54</v>
       </c>
       <c r="V50">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="W50">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X50">
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z50">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AA50">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB50">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AC50">
         <v>1.31</v>
@@ -8510,13 +8510,13 @@
         <v>2.92</v>
       </c>
       <c r="AE50">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.03</v>
       </c>
       <c r="AK50">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,37 +2265,37 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="O12">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="P12">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
         <v>1.26</v>
@@ -2304,25 +2304,25 @@
         <v>3.36</v>
       </c>
       <c r="AA12">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB12">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="AD12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,37 +2428,37 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O13">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q13">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="R13">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T13">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.26</v>
@@ -2467,25 +2467,25 @@
         <v>3.36</v>
       </c>
       <c r="AA13">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB13">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AC13">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
         <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AK13">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
+        <v>1.48</v>
+      </c>
+      <c r="O22">
+        <v>3.95</v>
+      </c>
+      <c r="P22">
+        <v>6</v>
+      </c>
+      <c r="Q22">
+        <v>2.02</v>
+      </c>
+      <c r="R22">
+        <v>2.22</v>
+      </c>
+      <c r="S22">
+        <v>1.37</v>
+      </c>
+      <c r="T22">
+        <v>2.78</v>
+      </c>
+      <c r="U22">
+        <v>2.74</v>
+      </c>
+      <c r="V22">
         <v>1.38</v>
       </c>
-      <c r="O22">
-        <v>4.45</v>
-      </c>
-      <c r="P22">
-        <v>6.6</v>
-      </c>
-      <c r="Q22">
-        <v>1.91</v>
-      </c>
-      <c r="R22">
-        <v>2.3</v>
-      </c>
-      <c r="S22">
-        <v>1.33</v>
-      </c>
-      <c r="T22">
-        <v>2.96</v>
-      </c>
-      <c r="U22">
-        <v>2.63</v>
-      </c>
-      <c r="V22">
-        <v>1.41</v>
-      </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB22">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AC22">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD22">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AG22">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK22">
-        <v>2.76</v>
+        <v>2.47</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="O23">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="Q23">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R23">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="U23">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="V23">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB23">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC23">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AD23">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AG23">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>2.47</v>
+        <v>2.76</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O49">
         <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q49">
         <v>2.83</v>
@@ -8314,13 +8314,13 @@
         <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U49">
         <v>2.27</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
         <v>1.1</v>
@@ -8341,19 +8341,19 @@
         <v>2.17</v>
       </c>
       <c r="AC49">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD49">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE49">
         <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8504,10 +8504,10 @@
         <v>6.5</v>
       </c>
       <c r="AC50">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD50">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AE50">
         <v>1.94</v>
@@ -8516,7 +8516,7 @@
         <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9">
@@ -1791,25 +1791,25 @@
         <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="U9">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V9">
         <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
         <v>3.1</v>
@@ -1818,7 +1818,7 @@
         <v>1.88</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AC9">
         <v>3.25</v>
@@ -1830,7 +1830,7 @@
         <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG9">
         <v>1.86</v>
@@ -1942,22 +1942,22 @@
         <v>3.2</v>
       </c>
       <c r="O10">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P10">
         <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>4.47</v>
+        <v>3.7</v>
       </c>
       <c r="R10">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S10">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="T10">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="U10">
         <v>4</v>
@@ -1972,16 +1972,16 @@
         <v>1.12</v>
       </c>
       <c r="Y10">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="Z10">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="AA10">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="AB10">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC10">
         <v>6.55</v>
@@ -1990,7 +1990,7 @@
         <v>1.05</v>
       </c>
       <c r="AE10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
         <v>2.41</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AK10">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="O16">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q16">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="U16">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC16">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
         <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q17">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="R17">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="U17">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA17">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB17">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -6825,23 +6825,23 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40">
+        <v>5.93</v>
+      </c>
+      <c r="O40">
+        <v>4.5</v>
+      </c>
+      <c r="P40">
+        <v>1.41</v>
+      </c>
+      <c r="Q40">
         <v>6</v>
       </c>
-      <c r="O40">
-        <v>4</v>
-      </c>
-      <c r="P40">
-        <v>1.44</v>
-      </c>
-      <c r="Q40">
-        <v>5.5</v>
-      </c>
       <c r="R40">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6850,22 +6850,22 @@
         <v>3.6</v>
       </c>
       <c r="U40">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="AA40">
         <v>1.53</v>
@@ -6877,7 +6877,7 @@
         <v>2.3</v>
       </c>
       <c r="AD40">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE40">
         <v>1.22</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AK40">
         <v>1.05</v>
@@ -8299,10 +8299,10 @@
         <v>2.25</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
         <v>2.83</v>
@@ -8341,13 +8341,13 @@
         <v>2.17</v>
       </c>
       <c r="AC49">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AD49">
         <v>1.5</v>
       </c>
       <c r="AE49">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF49">
         <v>1.44</v>
@@ -8462,10 +8462,10 @@
         <v>1.09</v>
       </c>
       <c r="O50">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="P50">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Q50">
         <v>1.3</v>
@@ -8495,25 +8495,25 @@
         <v>1.02</v>
       </c>
       <c r="Z50">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB50">
         <v>6.5</v>
       </c>
       <c r="AC50">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD50">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AE50">
         <v>1.94</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG50">
         <v>2.09</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O4">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="R4">
         <v>1.75</v>
@@ -979,7 +979,7 @@
         <v>1.57</v>
       </c>
       <c r="T4">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="U4">
         <v>4.1</v>
@@ -1006,7 +1006,7 @@
         <v>1.4</v>
       </c>
       <c r="AC4">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AD4">
         <v>1.09</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1302,16 +1302,16 @@
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T6">
         <v>3</v>
       </c>
       <c r="U6">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
         <v>1.07</v>
@@ -1320,13 +1320,13 @@
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
         <v>1.85</v>
@@ -1335,7 +1335,7 @@
         <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
         <v>1.08</v>
@@ -1344,7 +1344,7 @@
         <v>1.76</v>
       </c>
       <c r="AG6">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O10">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q10">
         <v>3.7</v>
@@ -1954,10 +1954,10 @@
         <v>1.65</v>
       </c>
       <c r="S10">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="T10">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
         <v>4</v>
@@ -1969,7 +1969,7 @@
         <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y10">
         <v>1.56</v>
@@ -1978,13 +1978,13 @@
         <v>1.79</v>
       </c>
       <c r="AA10">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AB10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC10">
-        <v>6.55</v>
+        <v>7.5</v>
       </c>
       <c r="AD10">
         <v>1.05</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q16">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
       <c r="R16">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
+        <v>1.5</v>
+      </c>
+      <c r="W16">
+        <v>1.11</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.18</v>
+      </c>
+      <c r="Z16">
+        <v>3.92</v>
+      </c>
+      <c r="AA16">
+        <v>1.66</v>
+      </c>
+      <c r="AB16">
+        <v>2.09</v>
+      </c>
+      <c r="AC16">
+        <v>2.68</v>
+      </c>
+      <c r="AD16">
+        <v>1.42</v>
+      </c>
+      <c r="AE16">
+        <v>1.14</v>
+      </c>
+      <c r="AF16">
+        <v>1.57</v>
+      </c>
+      <c r="AG16">
+        <v>2.26</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.5</v>
+      </c>
+      <c r="AK16">
         <v>1.4</v>
-      </c>
-      <c r="W16">
-        <v>1.08</v>
-      </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
-      <c r="Y16">
-        <v>1.22</v>
-      </c>
-      <c r="Z16">
-        <v>4.2</v>
-      </c>
-      <c r="AA16">
-        <v>1.75</v>
-      </c>
-      <c r="AB16">
-        <v>1.99</v>
-      </c>
-      <c r="AC16">
-        <v>2.83</v>
-      </c>
-      <c r="AD16">
-        <v>1.4</v>
-      </c>
-      <c r="AE16">
-        <v>1.08</v>
-      </c>
-      <c r="AF16">
-        <v>1.62</v>
-      </c>
-      <c r="AG16">
-        <v>2.2</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.22</v>
-      </c>
-      <c r="AK16">
-        <v>1.68</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,65 +3243,65 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
+        <v>3.1</v>
+      </c>
+      <c r="Q18">
+        <v>2.55</v>
+      </c>
+      <c r="R18">
+        <v>2.08</v>
+      </c>
+      <c r="S18">
+        <v>1.33</v>
+      </c>
+      <c r="T18">
+        <v>2.85</v>
+      </c>
+      <c r="U18">
+        <v>2.57</v>
+      </c>
+      <c r="V18">
+        <v>1.4</v>
+      </c>
+      <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1.04</v>
+      </c>
+      <c r="Y18">
+        <v>1.22</v>
+      </c>
+      <c r="Z18">
+        <v>4.2</v>
+      </c>
+      <c r="AA18">
+        <v>1.75</v>
+      </c>
+      <c r="AB18">
+        <v>1.99</v>
+      </c>
+      <c r="AC18">
+        <v>2.83</v>
+      </c>
+      <c r="AD18">
+        <v>1.4</v>
+      </c>
+      <c r="AE18">
+        <v>1.08</v>
+      </c>
+      <c r="AF18">
+        <v>1.62</v>
+      </c>
+      <c r="AG18">
         <v>2.2</v>
       </c>
-      <c r="Q18">
-        <v>3.53</v>
-      </c>
-      <c r="R18">
-        <v>2.12</v>
-      </c>
-      <c r="S18">
-        <v>1.29</v>
-      </c>
-      <c r="T18">
-        <v>3.12</v>
-      </c>
-      <c r="U18">
-        <v>2.48</v>
-      </c>
-      <c r="V18">
-        <v>1.5</v>
-      </c>
-      <c r="W18">
-        <v>1.11</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.18</v>
-      </c>
-      <c r="Z18">
-        <v>3.92</v>
-      </c>
-      <c r="AA18">
-        <v>1.66</v>
-      </c>
-      <c r="AB18">
-        <v>2.09</v>
-      </c>
-      <c r="AC18">
-        <v>2.68</v>
-      </c>
-      <c r="AD18">
-        <v>1.42</v>
-      </c>
-      <c r="AE18">
-        <v>1.14</v>
-      </c>
-      <c r="AF18">
-        <v>1.57</v>
-      </c>
-      <c r="AG18">
-        <v>2.26</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="O22">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="Q22">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R22">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="U22">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC22">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AD22">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AG22">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>2.47</v>
+        <v>2.76</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>1.48</v>
+      </c>
+      <c r="O23">
+        <v>3.95</v>
+      </c>
+      <c r="P23">
+        <v>6</v>
+      </c>
+      <c r="Q23">
+        <v>2.02</v>
+      </c>
+      <c r="R23">
+        <v>2.22</v>
+      </c>
+      <c r="S23">
+        <v>1.37</v>
+      </c>
+      <c r="T23">
+        <v>2.78</v>
+      </c>
+      <c r="U23">
+        <v>2.74</v>
+      </c>
+      <c r="V23">
         <v>1.38</v>
       </c>
-      <c r="O23">
-        <v>4.45</v>
-      </c>
-      <c r="P23">
-        <v>6.6</v>
-      </c>
-      <c r="Q23">
-        <v>1.91</v>
-      </c>
-      <c r="R23">
-        <v>2.3</v>
-      </c>
-      <c r="S23">
-        <v>1.33</v>
-      </c>
-      <c r="T23">
-        <v>2.96</v>
-      </c>
-      <c r="U23">
-        <v>2.63</v>
-      </c>
-      <c r="V23">
-        <v>1.41</v>
-      </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA23">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB23">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AC23">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD23">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AG23">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>2.76</v>
+        <v>2.47</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.35</v>
+        <v>2.73</v>
       </c>
       <c r="O27">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P27">
-        <v>2.73</v>
+        <v>2.37</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q28">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
         <v>1.33</v>
@@ -4906,13 +4906,13 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA28">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
         <v>1.85</v>
@@ -4921,7 +4921,7 @@
         <v>3.3</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G29">
@@ -5039,61 +5039,61 @@
         <v>2.3</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
       </c>
       <c r="R29">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="S29">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="U29">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
+        <v>1.04</v>
+      </c>
+      <c r="X29">
+        <v>1.03</v>
+      </c>
+      <c r="Y29">
+        <v>1.35</v>
+      </c>
+      <c r="Z29">
+        <v>2.74</v>
+      </c>
+      <c r="AA29">
+        <v>2.2</v>
+      </c>
+      <c r="AB29">
+        <v>1.65</v>
+      </c>
+      <c r="AC29">
+        <v>4.1</v>
+      </c>
+      <c r="AD29">
+        <v>1.18</v>
+      </c>
+      <c r="AE29">
         <v>1.02</v>
       </c>
-      <c r="X29">
-        <v>1.04</v>
-      </c>
-      <c r="Y29">
-        <v>1.33</v>
-      </c>
-      <c r="Z29">
-        <v>2.81</v>
-      </c>
-      <c r="AA29">
-        <v>2.12</v>
-      </c>
-      <c r="AB29">
-        <v>1.62</v>
-      </c>
-      <c r="AC29">
-        <v>3.72</v>
-      </c>
-      <c r="AD29">
-        <v>1.2</v>
-      </c>
-      <c r="AE29">
-        <v>1.03</v>
-      </c>
       <c r="AF29">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
-        <v>2.43</v>
+        <v>3.12</v>
       </c>
       <c r="R30">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="T30">
-        <v>2.77</v>
+        <v>2.32</v>
       </c>
       <c r="U30">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="V30">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="AA30">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="AB30">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AC30">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AD30">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG30">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R31">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T31">
         <v>2.5</v>
       </c>
       <c r="U31">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z31">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA31">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB31">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC31">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AD31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AG31">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.36</v>
       </c>
       <c r="AK31">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="O32">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R32">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="S32">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="U32">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="V32">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AA32">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AB32">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AC32">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD32">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
+        <v>1.95</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.17</v>
+      </c>
+      <c r="AK32">
         <v>1.8</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.28</v>
-      </c>
-      <c r="AK32">
-        <v>1.47</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
+        <v>3.1</v>
+      </c>
+      <c r="P33">
+        <v>2.5</v>
+      </c>
+      <c r="Q33">
+        <v>3.1</v>
+      </c>
+      <c r="R33">
+        <v>1.9</v>
+      </c>
+      <c r="S33">
+        <v>1.43</v>
+      </c>
+      <c r="T33">
+        <v>2.47</v>
+      </c>
+      <c r="U33">
         <v>3</v>
       </c>
-      <c r="P33">
-        <v>2.62</v>
-      </c>
-      <c r="Q33">
-        <v>3.15</v>
-      </c>
-      <c r="R33">
-        <v>2.01</v>
-      </c>
-      <c r="S33">
-        <v>1.49</v>
-      </c>
-      <c r="T33">
-        <v>2.45</v>
-      </c>
-      <c r="U33">
-        <v>3.4</v>
-      </c>
       <c r="V33">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA33">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC33">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG33">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
         <v>3</v>
       </c>
       <c r="P34">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="Q34">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R34">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S34">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T34">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U34">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="V34">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y34">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA34">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB34">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC34">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD34">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG34">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6041,7 +6041,7 @@
         <v>1.24</v>
       </c>
       <c r="W35">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
         <v>1.08</v>
@@ -6207,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="X36">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y36">
         <v>1.38</v>
@@ -6216,13 +6216,13 @@
         <v>2.62</v>
       </c>
       <c r="AA36">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AB36">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC36">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD36">
         <v>1.21</v>
@@ -6231,10 +6231,10 @@
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AG36">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6506,46 +6506,46 @@
         <v>1.36</v>
       </c>
       <c r="O38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P38">
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R38">
         <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T38">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="U38">
         <v>2.86</v>
       </c>
       <c r="V38">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z38">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA38">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB38">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC38">
         <v>4.1</v>
@@ -6557,10 +6557,10 @@
         <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AG38">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.04</v>
       </c>
       <c r="AK38">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7167,52 +7167,52 @@
         <v>3.75</v>
       </c>
       <c r="R42">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S42">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T42">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="U42">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="V42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W42">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z42">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AA42">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AB42">
         <v>1.5</v>
       </c>
       <c r="AC42">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="AD42">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE42">
         <v>1.02</v>
       </c>
       <c r="AF42">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG42">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>1.43</v>
       </c>
       <c r="T44">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="U44">
         <v>2.9</v>
@@ -7520,7 +7520,7 @@
         <v>3.03</v>
       </c>
       <c r="AA44">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB44">
         <v>1.68</v>
@@ -7535,7 +7535,7 @@
         <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
         <v>1.91</v>
@@ -7653,7 +7653,7 @@
         <v>2.65</v>
       </c>
       <c r="Q45">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="R45">
         <v>2.05</v>
@@ -7674,7 +7674,7 @@
         <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
         <v>1.36</v>
@@ -7683,25 +7683,25 @@
         <v>2.83</v>
       </c>
       <c r="AA45">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AB45">
         <v>1.63</v>
       </c>
       <c r="AC45">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AD45">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE45">
         <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG45">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.28</v>
       </c>
       <c r="AK45">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,16 +7816,16 @@
         <v>6</v>
       </c>
       <c r="Q46">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R46">
         <v>2.1</v>
       </c>
       <c r="S46">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T46">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U46">
         <v>3.2</v>
@@ -7834,16 +7834,16 @@
         <v>1.28</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z46">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA46">
         <v>2.13</v>
@@ -7852,19 +7852,19 @@
         <v>1.65</v>
       </c>
       <c r="AC46">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD46">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE46">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AG46">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>3</v>
       </c>
       <c r="P47">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q47">
         <v>3.94</v>
@@ -7991,10 +7991,10 @@
         <v>2.39</v>
       </c>
       <c r="U47">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="V47">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W47">
         <v>1.04</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
         <v>3.7</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="R3">
         <v>2.27</v>
       </c>
       <c r="S3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T3">
         <v>3.05</v>
@@ -831,19 +831,19 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z3">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="AA3">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB3">
         <v>2.02</v>
       </c>
       <c r="AC3">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="AD3">
         <v>1.35</v>
@@ -852,7 +852,7 @@
         <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG3">
         <v>2.02</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1127,61 +1127,61 @@
         <v>4.1</v>
       </c>
       <c r="O5">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q5">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="R5">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="U5">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z5">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AA5">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AB5">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AD5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AG5">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK5">
         <v>1.21</v>
@@ -1477,7 +1477,7 @@
         <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1492,22 +1492,22 @@
         <v>1.64</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
         <v>2.46</v>
       </c>
       <c r="AD7">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE7">
         <v>1.17</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         <v>3.3</v>
       </c>
       <c r="P8">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="Q8">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R8">
         <v>2.18</v>
@@ -1634,22 +1634,22 @@
         <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="AA8">
         <v>1.73</v>
@@ -1658,7 +1658,7 @@
         <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AD8">
         <v>1.36</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P11">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q11">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="R11">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U11">
         <v>2.75</v>
@@ -2141,10 +2141,10 @@
         <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC11">
         <v>3.28</v>
@@ -2156,10 +2156,10 @@
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG11">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,58 +2265,58 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O12">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q12">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S12">
         <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="AA12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
         <v>1.7</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AK12">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O13">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="P13">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S13">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="U13">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
         <v>1.07</v>
@@ -2461,32 +2461,32 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z13">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="AA13">
+        <v>1.93</v>
+      </c>
+      <c r="AB13">
+        <v>1.89</v>
+      </c>
+      <c r="AC13">
+        <v>3.56</v>
+      </c>
+      <c r="AD13">
+        <v>1.27</v>
+      </c>
+      <c r="AE13">
+        <v>1.05</v>
+      </c>
+      <c r="AF13">
+        <v>1.75</v>
+      </c>
+      <c r="AG13">
         <v>1.98</v>
       </c>
-      <c r="AB13">
-        <v>1.84</v>
-      </c>
-      <c r="AC13">
-        <v>3.05</v>
-      </c>
-      <c r="AD13">
-        <v>1.31</v>
-      </c>
-      <c r="AE13">
-        <v>1.13</v>
-      </c>
-      <c r="AF13">
-        <v>1.68</v>
-      </c>
-      <c r="AG13">
-        <v>2.08</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,31 +2594,31 @@
         <v>1.87</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
         <v>1.44</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.04</v>
@@ -2627,19 +2627,19 @@
         <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AA14">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AD14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
         <v>1.09</v>
@@ -2648,7 +2648,7 @@
         <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>3.4</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
         <v>1.85</v>
@@ -2793,16 +2793,16 @@
         <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC15">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
         <v>1.13</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
         <v>1.2</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q16">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
         <v>3.12</v>
       </c>
       <c r="U16">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
         <v>1.11</v>
@@ -2950,32 +2950,32 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AA16">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB16">
+        <v>2.08</v>
+      </c>
+      <c r="AC16">
+        <v>2.52</v>
+      </c>
+      <c r="AD16">
+        <v>1.44</v>
+      </c>
+      <c r="AE16">
+        <v>1.17</v>
+      </c>
+      <c r="AF16">
+        <v>1.62</v>
+      </c>
+      <c r="AG16">
         <v>2.09</v>
       </c>
-      <c r="AC16">
-        <v>2.68</v>
-      </c>
-      <c r="AD16">
-        <v>1.42</v>
-      </c>
-      <c r="AE16">
-        <v>1.14</v>
-      </c>
-      <c r="AF16">
-        <v>1.57</v>
-      </c>
-      <c r="AG16">
-        <v>2.26</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T17">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="U17">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB17">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC17">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O18">
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
       <c r="R18">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="U18">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="V18">
+        <v>1.5</v>
+      </c>
+      <c r="W18">
+        <v>1.11</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.18</v>
+      </c>
+      <c r="Z18">
+        <v>3.92</v>
+      </c>
+      <c r="AA18">
+        <v>1.66</v>
+      </c>
+      <c r="AB18">
+        <v>2.09</v>
+      </c>
+      <c r="AC18">
+        <v>2.69</v>
+      </c>
+      <c r="AD18">
+        <v>1.42</v>
+      </c>
+      <c r="AE18">
+        <v>1.14</v>
+      </c>
+      <c r="AF18">
+        <v>1.57</v>
+      </c>
+      <c r="AG18">
+        <v>2.26</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.41</v>
+      </c>
+      <c r="AK18">
         <v>1.4</v>
-      </c>
-      <c r="W18">
-        <v>1.08</v>
-      </c>
-      <c r="X18">
-        <v>1.04</v>
-      </c>
-      <c r="Y18">
-        <v>1.22</v>
-      </c>
-      <c r="Z18">
-        <v>4.2</v>
-      </c>
-      <c r="AA18">
-        <v>1.75</v>
-      </c>
-      <c r="AB18">
-        <v>1.99</v>
-      </c>
-      <c r="AC18">
-        <v>2.83</v>
-      </c>
-      <c r="AD18">
-        <v>1.4</v>
-      </c>
-      <c r="AE18">
-        <v>1.08</v>
-      </c>
-      <c r="AF18">
-        <v>1.62</v>
-      </c>
-      <c r="AG18">
-        <v>2.2</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.22</v>
-      </c>
-      <c r="AK18">
-        <v>1.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,16 +3415,16 @@
         <v>2.25</v>
       </c>
       <c r="Q19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U19">
         <v>2.58</v>
@@ -3445,7 +3445,7 @@
         <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB19">
         <v>1.9</v>
@@ -3454,13 +3454,13 @@
         <v>3.05</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
         <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG19">
         <v>2.05</v>
@@ -3479,7 +3479,7 @@
         <v>1.24</v>
       </c>
       <c r="AK19">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O20">
         <v>3.9</v>
       </c>
       <c r="P20">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
         <v>2.16</v>
@@ -3602,16 +3602,16 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC20">
         <v>2.83</v>
@@ -3642,7 +3642,7 @@
         <v>1.11</v>
       </c>
       <c r="AK20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="P21">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -3747,25 +3747,25 @@
         <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
         <v>3.3</v>
       </c>
       <c r="U21">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
         <v>1.53</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
         <v>4.5</v>
@@ -3777,19 +3777,19 @@
         <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AD21">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG21">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
         <v>2.1</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="O22">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="P22">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
+        <v>1.42</v>
+      </c>
+      <c r="T22">
+        <v>2.57</v>
+      </c>
+      <c r="U22">
+        <v>3.02</v>
+      </c>
+      <c r="V22">
+        <v>1.32</v>
+      </c>
+      <c r="W22">
+        <v>1.03</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
         <v>1.33</v>
       </c>
-      <c r="T22">
-        <v>2.96</v>
-      </c>
-      <c r="U22">
-        <v>2.63</v>
-      </c>
-      <c r="V22">
-        <v>1.41</v>
-      </c>
-      <c r="W22">
-        <v>1.06</v>
-      </c>
-      <c r="X22">
-        <v>1</v>
-      </c>
-      <c r="Y22">
-        <v>1.22</v>
-      </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AB22">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AC22">
-        <v>2.92</v>
+        <v>3.58</v>
       </c>
       <c r="AD22">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="AG22">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK22">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,61 +4058,61 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="O23">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="Q23">
+        <v>1.88</v>
+      </c>
+      <c r="R23">
+        <v>2.33</v>
+      </c>
+      <c r="S23">
+        <v>1.32</v>
+      </c>
+      <c r="T23">
+        <v>3.02</v>
+      </c>
+      <c r="U23">
+        <v>2.57</v>
+      </c>
+      <c r="V23">
+        <v>1.43</v>
+      </c>
+      <c r="W23">
+        <v>1.06</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
+        <v>1.21</v>
+      </c>
+      <c r="Z23">
+        <v>3.58</v>
+      </c>
+      <c r="AA23">
+        <v>1.81</v>
+      </c>
+      <c r="AB23">
         <v>2.02</v>
       </c>
-      <c r="R23">
-        <v>2.22</v>
-      </c>
-      <c r="S23">
-        <v>1.37</v>
-      </c>
-      <c r="T23">
-        <v>2.78</v>
-      </c>
-      <c r="U23">
-        <v>2.74</v>
-      </c>
-      <c r="V23">
-        <v>1.38</v>
-      </c>
-      <c r="W23">
-        <v>1.05</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>1.26</v>
-      </c>
-      <c r="Z23">
-        <v>3.2</v>
-      </c>
-      <c r="AA23">
-        <v>1.95</v>
-      </c>
-      <c r="AB23">
-        <v>1.88</v>
-      </c>
       <c r="AC23">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD23">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF23">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AG23">
         <v>1.72</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4543,38 +4543,38 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
         <v>1.2</v>
       </c>
       <c r="O26">
-        <v>5.25</v>
+        <v>5.7</v>
       </c>
       <c r="P26">
-        <v>9.75</v>
+        <v>13.6</v>
       </c>
       <c r="Q26">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R26">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="S26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T26">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="U26">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V26">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W26">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,28 +4583,28 @@
         <v>1.04</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA26">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB26">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC26">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AD26">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE26">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.03</v>
       </c>
       <c r="AK26">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O29">
         <v>3</v>
       </c>
       <c r="P29">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R29">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T29">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W29">
+        <v>1.02</v>
+      </c>
+      <c r="X29">
         <v>1.04</v>
       </c>
-      <c r="X29">
+      <c r="Y29">
+        <v>1.4</v>
+      </c>
+      <c r="Z29">
+        <v>2.88</v>
+      </c>
+      <c r="AA29">
+        <v>2.25</v>
+      </c>
+      <c r="AB29">
+        <v>1.57</v>
+      </c>
+      <c r="AC29">
+        <v>4.5</v>
+      </c>
+      <c r="AD29">
+        <v>1.2</v>
+      </c>
+      <c r="AE29">
         <v>1.03</v>
       </c>
-      <c r="Y29">
-        <v>1.35</v>
-      </c>
-      <c r="Z29">
-        <v>2.74</v>
-      </c>
-      <c r="AA29">
-        <v>2.2</v>
-      </c>
-      <c r="AB29">
-        <v>1.65</v>
-      </c>
-      <c r="AC29">
-        <v>4.1</v>
-      </c>
-      <c r="AD29">
-        <v>1.18</v>
-      </c>
-      <c r="AE29">
-        <v>1.02</v>
-      </c>
       <c r="AF29">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AG29">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G30">
@@ -5202,61 +5202,61 @@
         <v>2.3</v>
       </c>
       <c r="O30">
+        <v>3</v>
+      </c>
+      <c r="P30">
+        <v>2.8</v>
+      </c>
+      <c r="Q30">
         <v>3.1</v>
       </c>
-      <c r="P30">
-        <v>2.75</v>
-      </c>
-      <c r="Q30">
-        <v>3.12</v>
-      </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="S30">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
-        <v>2.32</v>
+        <v>2.61</v>
       </c>
       <c r="U30">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V30">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
+        <v>1.04</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.35</v>
+      </c>
+      <c r="Z30">
+        <v>2.74</v>
+      </c>
+      <c r="AA30">
+        <v>2.2</v>
+      </c>
+      <c r="AB30">
+        <v>1.65</v>
+      </c>
+      <c r="AC30">
+        <v>4.1</v>
+      </c>
+      <c r="AD30">
+        <v>1.18</v>
+      </c>
+      <c r="AE30">
         <v>1.02</v>
       </c>
-      <c r="X30">
-        <v>1.04</v>
-      </c>
-      <c r="Y30">
-        <v>1.34</v>
-      </c>
-      <c r="Z30">
-        <v>2.78</v>
-      </c>
-      <c r="AA30">
-        <v>2.13</v>
-      </c>
-      <c r="AB30">
-        <v>1.61</v>
-      </c>
-      <c r="AC30">
-        <v>3.74</v>
-      </c>
-      <c r="AD30">
-        <v>1.19</v>
-      </c>
-      <c r="AE30">
-        <v>1.03</v>
-      </c>
       <c r="AF30">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG30">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.6</v>
+        <v>1.81</v>
       </c>
       <c r="O31">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S31">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U31">
+        <v>2.59</v>
+      </c>
+      <c r="V31">
+        <v>1.42</v>
+      </c>
+      <c r="W31">
+        <v>1.07</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.3</v>
+      </c>
+      <c r="Z31">
         <v>3.4</v>
       </c>
-      <c r="V31">
-        <v>1.29</v>
-      </c>
-      <c r="W31">
-        <v>1.02</v>
-      </c>
-      <c r="X31">
-        <v>1.04</v>
-      </c>
-      <c r="Y31">
-        <v>1.4</v>
-      </c>
-      <c r="Z31">
-        <v>2.88</v>
-      </c>
       <c r="AA31">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB31">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AC31">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q32">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="R32">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T32">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="U32">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z32">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA32">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="AB32">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AC32">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE32">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q37">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R37">
         <v>2.02</v>
@@ -6358,13 +6358,13 @@
         <v>1.45</v>
       </c>
       <c r="T37">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U37">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="V37">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
         <v>1.07</v>
@@ -6388,7 +6388,7 @@
         <v>4.1</v>
       </c>
       <c r="AD37">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
         <v>1.07</v>
@@ -6397,7 +6397,7 @@
         <v>2.1</v>
       </c>
       <c r="AG37">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="O39">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="Q39">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R39">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S39">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T39">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U39">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.28</v>
+      </c>
+      <c r="Z39">
+        <v>3.24</v>
+      </c>
+      <c r="AA39">
+        <v>2.05</v>
+      </c>
+      <c r="AB39">
+        <v>1.82</v>
+      </c>
+      <c r="AC39">
+        <v>3.55</v>
+      </c>
+      <c r="AD39">
         <v>1.3</v>
       </c>
-      <c r="Z39">
-        <v>3.38</v>
-      </c>
-      <c r="AA39">
+      <c r="AE39">
+        <v>1.06</v>
+      </c>
+      <c r="AF39">
+        <v>1.74</v>
+      </c>
+      <c r="AG39">
         <v>2</v>
-      </c>
-      <c r="AB39">
-        <v>1.84</v>
-      </c>
-      <c r="AC39">
-        <v>3.67</v>
-      </c>
-      <c r="AD39">
-        <v>1.28</v>
-      </c>
-      <c r="AE39">
-        <v>1.05</v>
-      </c>
-      <c r="AF39">
-        <v>1.79</v>
-      </c>
-      <c r="AG39">
-        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
       <c r="O40">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P40">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Q40">
         <v>6</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6856,7 +6856,7 @@
         <v>1.55</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6865,7 +6865,7 @@
         <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>4.64</v>
+        <v>4.71</v>
       </c>
       <c r="AA40">
         <v>1.53</v>
@@ -6877,7 +6877,7 @@
         <v>2.3</v>
       </c>
       <c r="AD40">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE40">
         <v>1.22</v>
@@ -6995,16 +6995,16 @@
         <v>2.6</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q41">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="R41">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S41">
         <v>1.4</v>
@@ -7016,37 +7016,37 @@
         <v>2.88</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z41">
         <v>2.92</v>
       </c>
       <c r="AA41">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB41">
         <v>1.69</v>
       </c>
       <c r="AC41">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="AD41">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE41">
         <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG41">
         <v>1.93</v>
@@ -7336,13 +7336,13 @@
         <v>1.35</v>
       </c>
       <c r="T43">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="U43">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V43">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
         <v>1.1</v>
@@ -7357,16 +7357,16 @@
         <v>3.25</v>
       </c>
       <c r="AA43">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB43">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC43">
         <v>2.89</v>
       </c>
       <c r="AD43">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE43">
         <v>1.09</v>
@@ -7375,7 +7375,7 @@
         <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8139,7 +8139,7 @@
         <v>3.7</v>
       </c>
       <c r="P48">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -8154,13 +8154,13 @@
         <v>3.34</v>
       </c>
       <c r="U48">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V48">
         <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8172,22 +8172,22 @@
         <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB48">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="AD48">
         <v>1.47</v>
       </c>
       <c r="AE48">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG48">
         <v>2.3</v>
@@ -8299,7 +8299,7 @@
         <v>2.25</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
         <v>2.6</v>
@@ -8308,7 +8308,7 @@
         <v>2.83</v>
       </c>
       <c r="R49">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8323,13 +8323,13 @@
         <v>1.53</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
         <v>4.25</v>
@@ -8341,19 +8341,19 @@
         <v>2.17</v>
       </c>
       <c r="AC49">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD49">
+        <v>1.47</v>
+      </c>
+      <c r="AE49">
+        <v>1.17</v>
+      </c>
+      <c r="AF49">
         <v>1.5</v>
       </c>
-      <c r="AE49">
-        <v>1.2</v>
-      </c>
-      <c r="AF49">
-        <v>1.44</v>
-      </c>
       <c r="AG49">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
         <v>1.48</v>
@@ -8471,7 +8471,7 @@
         <v>1.3</v>
       </c>
       <c r="R50">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="S50">
         <v>1.08</v>
@@ -8480,10 +8480,10 @@
         <v>7.5</v>
       </c>
       <c r="U50">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V50">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="W50">
         <v>1.5</v>
@@ -8495,7 +8495,7 @@
         <v>1.02</v>
       </c>
       <c r="Z50">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AA50">
         <v>1.08</v>
@@ -8504,19 +8504,19 @@
         <v>6.5</v>
       </c>
       <c r="AC50">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AD50">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AE50">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AF50">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -644,7 +644,7 @@
         <v>5.82</v>
       </c>
       <c r="Q2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R2">
         <v>2.4</v>
@@ -656,10 +656,10 @@
         <v>2.99</v>
       </c>
       <c r="U2">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
         <v>1.1</v>
@@ -668,19 +668,19 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
         <v>4.17</v>
       </c>
       <c r="AA2">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB2">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AD2">
         <v>1.41</v>
@@ -689,7 +689,7 @@
         <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
         <v>1.86</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK2">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="P9">
-        <v>3.05</v>
+        <v>2.49</v>
       </c>
       <c r="Q9">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="T9">
-        <v>2.99</v>
+        <v>1.79</v>
       </c>
       <c r="U9">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="V9">
+        <v>1.17</v>
+      </c>
+      <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1.14</v>
+      </c>
+      <c r="Y9">
+        <v>1.56</v>
+      </c>
+      <c r="Z9">
+        <v>1.79</v>
+      </c>
+      <c r="AA9">
+        <v>3.22</v>
+      </c>
+      <c r="AB9">
+        <v>1.31</v>
+      </c>
+      <c r="AC9">
+        <v>7.5</v>
+      </c>
+      <c r="AD9">
+        <v>1.05</v>
+      </c>
+      <c r="AE9">
+        <v>1.01</v>
+      </c>
+      <c r="AF9">
+        <v>2.41</v>
+      </c>
+      <c r="AG9">
+        <v>1.48</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.4</v>
       </c>
-      <c r="W9">
-        <v>1.1</v>
-      </c>
-      <c r="X9">
-        <v>1.06</v>
-      </c>
-      <c r="Y9">
-        <v>1.22</v>
-      </c>
-      <c r="Z9">
-        <v>3.1</v>
-      </c>
-      <c r="AA9">
-        <v>1.88</v>
-      </c>
-      <c r="AB9">
-        <v>1.87</v>
-      </c>
-      <c r="AC9">
-        <v>3.25</v>
-      </c>
-      <c r="AD9">
-        <v>1.23</v>
-      </c>
-      <c r="AE9">
-        <v>1.06</v>
-      </c>
-      <c r="AF9">
-        <v>1.64</v>
-      </c>
-      <c r="AG9">
-        <v>1.86</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.3</v>
-      </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="P10">
-        <v>2.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q10">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="R10">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="S10">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
       <c r="U10">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="V10">
+        <v>1.4</v>
+      </c>
+      <c r="W10">
+        <v>1.08</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.26</v>
+      </c>
+      <c r="Z10">
+        <v>3.2</v>
+      </c>
+      <c r="AA10">
+        <v>1.95</v>
+      </c>
+      <c r="AB10">
+        <v>1.82</v>
+      </c>
+      <c r="AC10">
+        <v>3.28</v>
+      </c>
+      <c r="AD10">
+        <v>1.25</v>
+      </c>
+      <c r="AE10">
+        <v>1.05</v>
+      </c>
+      <c r="AF10">
+        <v>2.03</v>
+      </c>
+      <c r="AG10">
+        <v>1.69</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.17</v>
       </c>
-      <c r="W10">
-        <v>1.02</v>
-      </c>
-      <c r="X10">
-        <v>1.14</v>
-      </c>
-      <c r="Y10">
-        <v>1.56</v>
-      </c>
-      <c r="Z10">
-        <v>1.79</v>
-      </c>
-      <c r="AA10">
-        <v>3.22</v>
-      </c>
-      <c r="AB10">
-        <v>1.31</v>
-      </c>
-      <c r="AC10">
-        <v>7.5</v>
-      </c>
-      <c r="AD10">
-        <v>1.05</v>
-      </c>
-      <c r="AE10">
-        <v>1.01</v>
-      </c>
-      <c r="AF10">
-        <v>2.41</v>
-      </c>
-      <c r="AG10">
-        <v>1.48</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.4</v>
-      </c>
       <c r="AK10">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>2.83</v>
       </c>
       <c r="O11">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="P11">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="Q11">
-        <v>6.4</v>
+        <v>3.76</v>
       </c>
       <c r="R11">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="U11">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB11">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC11">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-17 12:00:00</t>
+          <t>2026-09-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="O13">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q13">
-        <v>3.76</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="AA13">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB13">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC13">
-        <v>3.56</v>
+        <v>2.81</v>
       </c>
       <c r="AD13">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF13">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-17 12:30:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.87</v>
+        <v>3.4</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="Q14">
+        <v>4</v>
+      </c>
+      <c r="R14">
         <v>2.3</v>
-      </c>
-      <c r="R14">
-        <v>2.12</v>
       </c>
       <c r="S14">
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="V14">
         <v>1.44</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA14">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q15">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U15">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W15">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AA15">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB15">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC15">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AD15">
         <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="P16">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="AA16">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB16">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3690,22 +3690,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.67</v>
+        <v>2.11</v>
       </c>
       <c r="O21">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q21">
+        <v>2.63</v>
+      </c>
+      <c r="R21">
         <v>2.1</v>
       </c>
-      <c r="R21">
-        <v>2.4</v>
-      </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U21">
-        <v>2.32</v>
+        <v>2.73</v>
       </c>
       <c r="V21">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z21">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA21">
+        <v>1.88</v>
+      </c>
+      <c r="AB21">
+        <v>1.83</v>
+      </c>
+      <c r="AC21">
+        <v>3.25</v>
+      </c>
+      <c r="AD21">
+        <v>1.23</v>
+      </c>
+      <c r="AE21">
+        <v>1.06</v>
+      </c>
+      <c r="AF21">
+        <v>1.63</v>
+      </c>
+      <c r="AG21">
+        <v>1.86</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.3</v>
+      </c>
+      <c r="AK21">
         <v>1.65</v>
-      </c>
-      <c r="AB21">
-        <v>2.2</v>
-      </c>
-      <c r="AC21">
-        <v>2.46</v>
-      </c>
-      <c r="AD21">
-        <v>1.43</v>
-      </c>
-      <c r="AE21">
-        <v>1.2</v>
-      </c>
-      <c r="AF21">
-        <v>1.6</v>
-      </c>
-      <c r="AG21">
-        <v>2.15</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.18</v>
-      </c>
-      <c r="AK21">
-        <v>2.1</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="O22">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="Q22">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="S22">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T22">
+        <v>3.02</v>
+      </c>
+      <c r="U22">
         <v>2.57</v>
       </c>
-      <c r="U22">
-        <v>3.02</v>
-      </c>
       <c r="V22">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1.03</v>
       </c>
       <c r="Y22">
+        <v>1.21</v>
+      </c>
+      <c r="Z22">
+        <v>3.58</v>
+      </c>
+      <c r="AA22">
+        <v>1.81</v>
+      </c>
+      <c r="AB22">
+        <v>2.02</v>
+      </c>
+      <c r="AC22">
+        <v>2.83</v>
+      </c>
+      <c r="AD22">
         <v>1.33</v>
       </c>
-      <c r="Z22">
-        <v>2.83</v>
-      </c>
-      <c r="AA22">
-        <v>2.14</v>
-      </c>
-      <c r="AB22">
+      <c r="AE22">
+        <v>1.09</v>
+      </c>
+      <c r="AF22">
+        <v>1.98</v>
+      </c>
+      <c r="AG22">
         <v>1.72</v>
       </c>
-      <c r="AC22">
-        <v>3.58</v>
-      </c>
-      <c r="AD22">
-        <v>1.21</v>
-      </c>
-      <c r="AE22">
-        <v>1.04</v>
-      </c>
-      <c r="AF22">
-        <v>2.16</v>
-      </c>
-      <c r="AG22">
-        <v>1.62</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="O23">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="P23">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
+        <v>1.42</v>
+      </c>
+      <c r="T23">
+        <v>2.57</v>
+      </c>
+      <c r="U23">
+        <v>3.02</v>
+      </c>
+      <c r="V23">
         <v>1.32</v>
       </c>
-      <c r="T23">
-        <v>3.02</v>
-      </c>
-      <c r="U23">
-        <v>2.57</v>
-      </c>
-      <c r="V23">
-        <v>1.43</v>
-      </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
         <v>1.03</v>
       </c>
       <c r="Y23">
+        <v>1.33</v>
+      </c>
+      <c r="Z23">
+        <v>2.83</v>
+      </c>
+      <c r="AA23">
+        <v>2.14</v>
+      </c>
+      <c r="AB23">
+        <v>1.72</v>
+      </c>
+      <c r="AC23">
+        <v>3.58</v>
+      </c>
+      <c r="AD23">
         <v>1.21</v>
       </c>
-      <c r="Z23">
-        <v>3.58</v>
-      </c>
-      <c r="AA23">
-        <v>1.81</v>
-      </c>
-      <c r="AB23">
-        <v>2.02</v>
-      </c>
-      <c r="AC23">
-        <v>2.83</v>
-      </c>
-      <c r="AD23">
-        <v>1.33</v>
-      </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="AG23">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="O24">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="P24">
-        <v>10.53</v>
+        <v>14</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4396,13 +4396,13 @@
         <v>1.91</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
         <v>2.2</v>
@@ -4423,13 +4423,13 @@
         <v>4.6</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AB25">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AC25">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AD25">
         <v>1.56</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G30">
@@ -5202,61 +5202,61 @@
         <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R30">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="S30">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T30">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="U30">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W30">
+        <v>1.02</v>
+      </c>
+      <c r="X30">
         <v>1.04</v>
       </c>
-      <c r="X30">
+      <c r="Y30">
+        <v>1.34</v>
+      </c>
+      <c r="Z30">
+        <v>2.78</v>
+      </c>
+      <c r="AA30">
+        <v>2.13</v>
+      </c>
+      <c r="AB30">
+        <v>1.61</v>
+      </c>
+      <c r="AC30">
+        <v>3.74</v>
+      </c>
+      <c r="AD30">
+        <v>1.19</v>
+      </c>
+      <c r="AE30">
         <v>1.03</v>
       </c>
-      <c r="Y30">
-        <v>1.35</v>
-      </c>
-      <c r="Z30">
-        <v>2.74</v>
-      </c>
-      <c r="AA30">
-        <v>2.2</v>
-      </c>
-      <c r="AB30">
-        <v>1.65</v>
-      </c>
-      <c r="AC30">
-        <v>4.1</v>
-      </c>
-      <c r="AD30">
-        <v>1.18</v>
-      </c>
-      <c r="AE30">
-        <v>1.02</v>
-      </c>
       <c r="AF30">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG30">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q31">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="U31">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z31">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AA31">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AB31">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q32">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="R32">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="S32">
         <v>1.49</v>
       </c>
       <c r="T32">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="U32">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="V32">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y32">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z32">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AA32">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AB32">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC32">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="AD32">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF32">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG32">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
         <v>1.5</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="S33">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="U33">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB33">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE33">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O34">
+        <v>3.1</v>
+      </c>
+      <c r="P34">
+        <v>2.5</v>
+      </c>
+      <c r="Q34">
+        <v>3.1</v>
+      </c>
+      <c r="R34">
+        <v>1.9</v>
+      </c>
+      <c r="S34">
+        <v>1.43</v>
+      </c>
+      <c r="T34">
+        <v>2.47</v>
+      </c>
+      <c r="U34">
         <v>3</v>
       </c>
-      <c r="P34">
-        <v>2.7</v>
-      </c>
-      <c r="Q34">
-        <v>3.15</v>
-      </c>
-      <c r="R34">
-        <v>2.01</v>
-      </c>
-      <c r="S34">
-        <v>1.49</v>
-      </c>
-      <c r="T34">
-        <v>2.45</v>
-      </c>
-      <c r="U34">
-        <v>3.4</v>
-      </c>
       <c r="V34">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
         <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z34">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AA34">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AB34">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC34">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG34">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
         <v>3.75</v>
@@ -6349,37 +6349,37 @@
         <v>5.6</v>
       </c>
       <c r="Q37">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="R37">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S37">
         <v>1.45</v>
       </c>
       <c r="T37">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="U37">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="V37">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W37">
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AA37">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AB37">
         <v>1.67</v>
@@ -6388,7 +6388,7 @@
         <v>4.1</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
         <v>1.07</v>
@@ -6397,7 +6397,7 @@
         <v>2.1</v>
       </c>
       <c r="AG37">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6995,16 +6995,16 @@
         <v>2.6</v>
       </c>
       <c r="O41">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
         <v>2.45</v>
       </c>
       <c r="Q41">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="R41">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="S41">
         <v>1.4</v>
@@ -7013,19 +7013,19 @@
         <v>2.62</v>
       </c>
       <c r="U41">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
         <v>1.03</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
         <v>2.92</v>
@@ -7034,10 +7034,10 @@
         <v>2.02</v>
       </c>
       <c r="AB41">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC41">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="AD41">
         <v>1.22</v>
@@ -7046,10 +7046,10 @@
         <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>2.2</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
         <v>3.15</v>
@@ -7357,7 +7357,7 @@
         <v>3.25</v>
       </c>
       <c r="AA43">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
         <v>2</v>
@@ -7366,7 +7366,7 @@
         <v>2.89</v>
       </c>
       <c r="AD43">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE43">
         <v>1.09</v>
@@ -7391,7 +7391,7 @@
         <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O44">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P44">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="Q44">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="R44">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="U44">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V44">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W44">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z44">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="AA44">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AB44">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC44">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AD44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG44">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O45">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="Q45">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="R45">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S45">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T45">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="U45">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V45">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
+        <v>1.32</v>
+      </c>
+      <c r="Z45">
+        <v>3.03</v>
+      </c>
+      <c r="AA45">
+        <v>2.08</v>
+      </c>
+      <c r="AB45">
+        <v>1.68</v>
+      </c>
+      <c r="AC45">
+        <v>4.1</v>
+      </c>
+      <c r="AD45">
+        <v>1.22</v>
+      </c>
+      <c r="AE45">
+        <v>1.07</v>
+      </c>
+      <c r="AF45">
+        <v>1.8</v>
+      </c>
+      <c r="AG45">
+        <v>1.91</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>1.33</v>
+      </c>
+      <c r="AK45">
         <v>1.36</v>
-      </c>
-      <c r="Z45">
-        <v>2.83</v>
-      </c>
-      <c r="AA45">
-        <v>2.12</v>
-      </c>
-      <c r="AB45">
-        <v>1.63</v>
-      </c>
-      <c r="AC45">
-        <v>3.82</v>
-      </c>
-      <c r="AD45">
-        <v>1.18</v>
-      </c>
-      <c r="AE45">
-        <v>1.02</v>
-      </c>
-      <c r="AF45">
-        <v>1.85</v>
-      </c>
-      <c r="AG45">
-        <v>1.79</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.28</v>
-      </c>
-      <c r="AK45">
-        <v>1.58</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8154,7 +8154,7 @@
         <v>3.34</v>
       </c>
       <c r="U48">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
         <v>1.5</v>
@@ -8166,16 +8166,16 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
         <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB48">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC48">
         <v>2.43</v>
@@ -8184,7 +8184,7 @@
         <v>1.47</v>
       </c>
       <c r="AE48">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
         <v>1.54</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
         <v>1.29</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="R6">
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,37 +2102,37 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="O11">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="P11">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q11">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="R11">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
+        <v>1.38</v>
+      </c>
+      <c r="T11">
+        <v>3.01</v>
+      </c>
+      <c r="U11">
+        <v>2.85</v>
+      </c>
+      <c r="V11">
         <v>1.4</v>
       </c>
-      <c r="T11">
-        <v>2.86</v>
-      </c>
-      <c r="U11">
-        <v>2.82</v>
-      </c>
-      <c r="V11">
-        <v>1.41</v>
-      </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.28</v>
@@ -2141,25 +2141,25 @@
         <v>3.24</v>
       </c>
       <c r="AA11">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC11">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,37 +2265,37 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O12">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="P12">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="R12">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>3.01</v>
+        <v>2.86</v>
       </c>
       <c r="U12">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.28</v>
@@ -2304,25 +2304,25 @@
         <v>3.24</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="AD12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q28">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="R28">
         <v>2.2</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="U28">
         <v>2.88</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
         <v>1.06</v>
@@ -4906,31 +4906,31 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB28">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC28">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG28">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,31 +5036,31 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O29">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q29">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S29">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="U29">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="V29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
         <v>1.02</v>
@@ -5069,31 +5069,31 @@
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z29">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA29">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC29">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AD29">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE29">
         <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG29">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK29">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G30">
@@ -5202,61 +5202,61 @@
         <v>2.3</v>
       </c>
       <c r="O30">
+        <v>3</v>
+      </c>
+      <c r="P30">
+        <v>2.8</v>
+      </c>
+      <c r="Q30">
         <v>3.1</v>
       </c>
-      <c r="P30">
-        <v>2.75</v>
-      </c>
-      <c r="Q30">
-        <v>3.12</v>
-      </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="S30">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
-        <v>2.32</v>
+        <v>2.61</v>
       </c>
       <c r="U30">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V30">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
+        <v>1.04</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.35</v>
+      </c>
+      <c r="Z30">
+        <v>2.74</v>
+      </c>
+      <c r="AA30">
+        <v>2.2</v>
+      </c>
+      <c r="AB30">
+        <v>1.65</v>
+      </c>
+      <c r="AC30">
+        <v>4.1</v>
+      </c>
+      <c r="AD30">
+        <v>1.18</v>
+      </c>
+      <c r="AE30">
         <v>1.02</v>
       </c>
-      <c r="X30">
-        <v>1.04</v>
-      </c>
-      <c r="Y30">
-        <v>1.34</v>
-      </c>
-      <c r="Z30">
-        <v>2.78</v>
-      </c>
-      <c r="AA30">
-        <v>2.13</v>
-      </c>
-      <c r="AB30">
-        <v>1.61</v>
-      </c>
-      <c r="AC30">
-        <v>3.74</v>
-      </c>
-      <c r="AD30">
-        <v>1.19</v>
-      </c>
-      <c r="AE30">
-        <v>1.03</v>
-      </c>
       <c r="AF30">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG30">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,61 +5362,61 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
         <v>3</v>
       </c>
       <c r="P31">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R31">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T31">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="U31">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y31">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z31">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA31">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB31">
         <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AG31">
         <v>1.8</v>
@@ -5435,7 +5435,7 @@
         <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="O32">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="R32">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="S32">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="U32">
+        <v>2.59</v>
+      </c>
+      <c r="V32">
+        <v>1.42</v>
+      </c>
+      <c r="W32">
+        <v>1.07</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.3</v>
+      </c>
+      <c r="Z32">
         <v>3.4</v>
       </c>
-      <c r="V32">
-        <v>1.29</v>
-      </c>
-      <c r="W32">
-        <v>1.05</v>
-      </c>
-      <c r="X32">
+      <c r="AA32">
+        <v>1.92</v>
+      </c>
+      <c r="AB32">
+        <v>1.81</v>
+      </c>
+      <c r="AC32">
+        <v>3.4</v>
+      </c>
+      <c r="AD32">
+        <v>1.3</v>
+      </c>
+      <c r="AE32">
         <v>1.07</v>
       </c>
-      <c r="Y32">
-        <v>1.4</v>
-      </c>
-      <c r="Z32">
-        <v>2.75</v>
-      </c>
-      <c r="AA32">
-        <v>2.17</v>
-      </c>
-      <c r="AB32">
-        <v>1.65</v>
-      </c>
-      <c r="AC32">
-        <v>4.5</v>
-      </c>
-      <c r="AD32">
-        <v>1.2</v>
-      </c>
-      <c r="AE32">
-        <v>1.01</v>
-      </c>
       <c r="AF32">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
+        <v>1.95</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.17</v>
+      </c>
+      <c r="AK32">
         <v>1.8</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.29</v>
-      </c>
-      <c r="AK32">
-        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="P33">
+        <v>2.4</v>
+      </c>
+      <c r="Q33">
         <v>3.6</v>
       </c>
-      <c r="P33">
-        <v>4.2</v>
-      </c>
-      <c r="Q33">
-        <v>2.45</v>
-      </c>
       <c r="R33">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S33">
+        <v>1.46</v>
+      </c>
+      <c r="T33">
+        <v>2.5</v>
+      </c>
+      <c r="U33">
+        <v>3.4</v>
+      </c>
+      <c r="V33">
+        <v>1.29</v>
+      </c>
+      <c r="W33">
+        <v>1.02</v>
+      </c>
+      <c r="X33">
+        <v>1.04</v>
+      </c>
+      <c r="Y33">
+        <v>1.4</v>
+      </c>
+      <c r="Z33">
+        <v>2.88</v>
+      </c>
+      <c r="AA33">
+        <v>2.25</v>
+      </c>
+      <c r="AB33">
+        <v>1.57</v>
+      </c>
+      <c r="AC33">
+        <v>4.5</v>
+      </c>
+      <c r="AD33">
+        <v>1.2</v>
+      </c>
+      <c r="AE33">
+        <v>1.03</v>
+      </c>
+      <c r="AF33">
+        <v>1.93</v>
+      </c>
+      <c r="AG33">
+        <v>1.75</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.36</v>
       </c>
-      <c r="T33">
-        <v>2.73</v>
-      </c>
-      <c r="U33">
-        <v>2.59</v>
-      </c>
-      <c r="V33">
-        <v>1.42</v>
-      </c>
-      <c r="W33">
-        <v>1.07</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.3</v>
-      </c>
-      <c r="Z33">
-        <v>3.4</v>
-      </c>
-      <c r="AA33">
-        <v>1.92</v>
-      </c>
-      <c r="AB33">
-        <v>1.81</v>
-      </c>
-      <c r="AC33">
-        <v>3.4</v>
-      </c>
-      <c r="AD33">
-        <v>1.3</v>
-      </c>
-      <c r="AE33">
-        <v>1.07</v>
-      </c>
-      <c r="AF33">
-        <v>1.75</v>
-      </c>
-      <c r="AG33">
-        <v>1.95</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.17</v>
-      </c>
       <c r="AK33">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -631,111 +631,111 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O2">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="P2">
-        <v>5.82</v>
+        <v>6.5</v>
       </c>
       <c r="Q2">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T2">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="U2">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z2">
-        <v>4.17</v>
+        <v>4.3</v>
       </c>
       <c r="AA2">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AB2">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC2">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="AD2">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
         <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "39", "41"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "25"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK2">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -794,35 +794,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P3">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q3">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="R3">
         <v>2.27</v>
       </c>
       <c r="S3">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="U3">
         <v>2.51</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.1</v>
@@ -831,19 +831,19 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z3">
-        <v>3.92</v>
+        <v>3.68</v>
       </c>
       <c r="AA3">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB3">
         <v>2.02</v>
       </c>
       <c r="AC3">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AD3">
         <v>1.35</v>
@@ -852,7 +852,7 @@
         <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
         <v>2.02</v>
@@ -868,37 +868,37 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <v>2.8</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q4">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R4">
         <v>1.75</v>
@@ -979,10 +979,10 @@
         <v>1.57</v>
       </c>
       <c r="T4">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U4">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="V4">
         <v>1.19</v>
@@ -994,10 +994,10 @@
         <v>1.1</v>
       </c>
       <c r="Y4">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z4">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AA4">
         <v>2.7</v>
@@ -1018,7 +1018,7 @@
         <v>2.32</v>
       </c>
       <c r="AG4">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1104,45 +1104,45 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="Q5">
-        <v>5.27</v>
+        <v>4.6</v>
       </c>
       <c r="R5">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S5">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T5">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="U5">
         <v>3.12</v>
@@ -1151,25 +1151,25 @@
         <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z5">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="AA5">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AD5">
         <v>1.18</v>
@@ -1178,10 +1178,10 @@
         <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AG5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1190,41 +1190,41 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "84"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="AK5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "50", "90+2"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1446,65 +1446,65 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="O7">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
         <v>2.95</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA7">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC7">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AD7">
         <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG7">
         <v>2.3</v>
@@ -1516,41 +1516,41 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "40"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1619,62 +1619,62 @@
         <v>3.3</v>
       </c>
       <c r="P8">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="Q8">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R8">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S8">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AA8">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1683,37 +1683,37 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1772,20 +1772,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N9">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="O9">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="P9">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="Q9">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R9">
         <v>1.65</v>
@@ -1794,7 +1794,7 @@
         <v>1.67</v>
       </c>
       <c r="T9">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="U9">
         <v>4</v>
@@ -1809,31 +1809,31 @@
         <v>1.14</v>
       </c>
       <c r="Y9">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="Z9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AA9">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="AB9">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AC9">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD9">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AG9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1919,45 +1919,45 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O10">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q10">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="R10">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="S10">
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="U10">
         <v>2.75</v>
@@ -1969,34 +1969,34 @@
         <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB10">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC10">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG10">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2005,41 +2005,41 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "54", "90+2"]</t>
         </is>
       </c>
       <c r="AJ10">
         <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="O11">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q11">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="R11">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="U11">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z11">
+        <v>3</v>
+      </c>
+      <c r="AA11">
+        <v>2</v>
+      </c>
+      <c r="AB11">
+        <v>1.86</v>
+      </c>
+      <c r="AC11">
         <v>3.24</v>
-      </c>
-      <c r="AA11">
-        <v>1.95</v>
-      </c>
-      <c r="AB11">
-        <v>1.87</v>
-      </c>
-      <c r="AC11">
-        <v>3.2</v>
       </c>
       <c r="AD11">
         <v>1.28</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AK11">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="P12">
         <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="R12">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="S12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="U12">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1.25</v>
+      </c>
+      <c r="Z12">
+        <v>3.44</v>
+      </c>
+      <c r="AA12">
+        <v>1.92</v>
+      </c>
+      <c r="AB12">
+        <v>1.94</v>
+      </c>
+      <c r="AC12">
+        <v>3.19</v>
+      </c>
+      <c r="AD12">
+        <v>1.37</v>
+      </c>
+      <c r="AE12">
         <v>1.07</v>
       </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>1.28</v>
-      </c>
-      <c r="Z12">
-        <v>3.24</v>
-      </c>
-      <c r="AA12">
-        <v>1.93</v>
-      </c>
-      <c r="AB12">
-        <v>1.89</v>
-      </c>
-      <c r="AC12">
-        <v>3.56</v>
-      </c>
-      <c r="AD12">
-        <v>1.27</v>
-      </c>
-      <c r="AE12">
-        <v>1.05</v>
-      </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG12">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O17">
         <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q17">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
       <c r="R17">
+        <v>2.12</v>
+      </c>
+      <c r="S17">
+        <v>1.3</v>
+      </c>
+      <c r="T17">
+        <v>3.12</v>
+      </c>
+      <c r="U17">
+        <v>2.48</v>
+      </c>
+      <c r="V17">
+        <v>1.5</v>
+      </c>
+      <c r="W17">
+        <v>1.11</v>
+      </c>
+      <c r="X17">
+        <v>1.02</v>
+      </c>
+      <c r="Y17">
+        <v>1.18</v>
+      </c>
+      <c r="Z17">
+        <v>3.92</v>
+      </c>
+      <c r="AA17">
+        <v>1.66</v>
+      </c>
+      <c r="AB17">
         <v>2.09</v>
       </c>
-      <c r="S17">
-        <v>1.32</v>
-      </c>
-      <c r="T17">
-        <v>2.89</v>
-      </c>
-      <c r="U17">
-        <v>2.57</v>
-      </c>
-      <c r="V17">
+      <c r="AC17">
+        <v>2.69</v>
+      </c>
+      <c r="AD17">
+        <v>1.42</v>
+      </c>
+      <c r="AE17">
+        <v>1.14</v>
+      </c>
+      <c r="AF17">
+        <v>1.57</v>
+      </c>
+      <c r="AG17">
+        <v>2.26</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.41</v>
+      </c>
+      <c r="AK17">
         <v>1.4</v>
-      </c>
-      <c r="W17">
-        <v>1.08</v>
-      </c>
-      <c r="X17">
-        <v>1.04</v>
-      </c>
-      <c r="Y17">
-        <v>1.22</v>
-      </c>
-      <c r="Z17">
-        <v>4.2</v>
-      </c>
-      <c r="AA17">
-        <v>1.73</v>
-      </c>
-      <c r="AB17">
-        <v>1.99</v>
-      </c>
-      <c r="AC17">
-        <v>2.83</v>
-      </c>
-      <c r="AD17">
-        <v>1.4</v>
-      </c>
-      <c r="AE17">
-        <v>1.09</v>
-      </c>
-      <c r="AF17">
-        <v>1.62</v>
-      </c>
-      <c r="AG17">
-        <v>2.2</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.22</v>
-      </c>
-      <c r="AK17">
-        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O18">
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q18">
-        <v>3.53</v>
+        <v>2.55</v>
       </c>
       <c r="R18">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="U18">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB18">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AC18">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD18">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O22">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="P22">
         <v>6.8</v>
       </c>
       <c r="Q22">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R22">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T22">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U22">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z22">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA22">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB22">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC22">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AD22">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AG22">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="O23">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="Q23">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S23">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T23">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="U23">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="V23">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z23">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AA23">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AB23">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AC23">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AD23">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AG23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AK23">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
+        <v>2.05</v>
+      </c>
+      <c r="Q28">
+        <v>4.33</v>
+      </c>
+      <c r="R28">
         <v>2</v>
       </c>
-      <c r="Q28">
-        <v>4.3</v>
-      </c>
-      <c r="R28">
-        <v>2.2</v>
-      </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V28">
         <v>1.33</v>
       </c>
       <c r="W28">
+        <v>1.05</v>
+      </c>
+      <c r="X28">
         <v>1.06</v>
       </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA28">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB28">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC28">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="AD28">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG28">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q29">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="R29">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T29">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="U29">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z29">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AA29">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC29">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AD29">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE29">
         <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O30">
         <v>3</v>
       </c>
       <c r="P30">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R30">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="S30">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T30">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="U30">
         <v>3.1</v>
@@ -5229,34 +5229,34 @@
         <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA30">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC30">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD30">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE30">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF30">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG30">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="O31">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="Q31">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="R31">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="U31">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="V31">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA31">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC31">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE31">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q32">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="R32">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="T32">
-        <v>2.73</v>
+        <v>2.34</v>
       </c>
       <c r="U32">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z32">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA32">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="AB32">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AC32">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE32">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
+        <v>2.5</v>
+      </c>
+      <c r="O33">
+        <v>3.1</v>
+      </c>
+      <c r="P33">
         <v>2.6</v>
       </c>
-      <c r="O33">
-        <v>3</v>
-      </c>
-      <c r="P33">
-        <v>2.4</v>
-      </c>
       <c r="Q33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R33">
         <v>2</v>
@@ -5706,46 +5706,46 @@
         <v>1.46</v>
       </c>
       <c r="T33">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U33">
         <v>3.4</v>
       </c>
       <c r="V33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z33">
         <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB33">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC33">
         <v>4.5</v>
       </c>
       <c r="AD33">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE33">
         <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK33">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>2.5</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R34">
         <v>1.9</v>
@@ -5872,10 +5872,10 @@
         <v>2.47</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W34">
         <v>1.05</v>
@@ -5884,31 +5884,31 @@
         <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z34">
         <v>2.78</v>
       </c>
       <c r="AA34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB34">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC34">
         <v>3.58</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE34">
         <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG34">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>7.7</v>
+        <v>7.62</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="Q36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
         <v>1.5</v>
       </c>
       <c r="T36">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="U36">
         <v>3.3</v>
       </c>
       <c r="V36">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X36">
+        <v>1.06</v>
+      </c>
+      <c r="Y36">
+        <v>1.32</v>
+      </c>
+      <c r="Z36">
+        <v>2.88</v>
+      </c>
+      <c r="AA36">
+        <v>2.06</v>
+      </c>
+      <c r="AB36">
+        <v>1.57</v>
+      </c>
+      <c r="AC36">
+        <v>3.68</v>
+      </c>
+      <c r="AD36">
+        <v>1.26</v>
+      </c>
+      <c r="AE36">
         <v>1.07</v>
       </c>
-      <c r="Y36">
-        <v>1.38</v>
-      </c>
-      <c r="Z36">
-        <v>2.62</v>
-      </c>
-      <c r="AA36">
-        <v>2.24</v>
-      </c>
-      <c r="AB36">
-        <v>1.55</v>
-      </c>
-      <c r="AC36">
-        <v>4.2</v>
-      </c>
-      <c r="AD36">
-        <v>1.21</v>
-      </c>
-      <c r="AE36">
-        <v>1.06</v>
-      </c>
       <c r="AF36">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AG36">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>2.78</v>
       </c>
       <c r="AK36">
         <v>1.1</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O39">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P39">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="Q39">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="R39">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U39">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W39">
         <v>1.05</v>
@@ -6699,31 +6699,31 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC39">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="AD39">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AK39">
         <v>1.39</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O44">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="R44">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S44">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T44">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="U44">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V44">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA44">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB44">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC44">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD44">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE44">
         <v>1.02</v>
       </c>
       <c r="AF44">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK44">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,65 +7644,65 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="O45">
         <v>3.1</v>
       </c>
       <c r="P45">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="Q45">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="R45">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S45">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="U45">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V45">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W45">
         <v>1.01</v>
       </c>
       <c r="X45">
+        <v>1.06</v>
+      </c>
+      <c r="Y45">
+        <v>1.36</v>
+      </c>
+      <c r="Z45">
+        <v>2.83</v>
+      </c>
+      <c r="AA45">
+        <v>2.11</v>
+      </c>
+      <c r="AB45">
+        <v>1.62</v>
+      </c>
+      <c r="AC45">
+        <v>3.8</v>
+      </c>
+      <c r="AD45">
+        <v>1.19</v>
+      </c>
+      <c r="AE45">
         <v>1.02</v>
       </c>
-      <c r="Y45">
-        <v>1.32</v>
-      </c>
-      <c r="Z45">
-        <v>3.03</v>
-      </c>
-      <c r="AA45">
-        <v>2.08</v>
-      </c>
-      <c r="AB45">
-        <v>1.68</v>
-      </c>
-      <c r="AC45">
-        <v>4.1</v>
-      </c>
-      <c r="AD45">
-        <v>1.22</v>
-      </c>
-      <c r="AE45">
-        <v>1.07</v>
-      </c>
       <c r="AF45">
+        <v>1.84</v>
+      </c>
+      <c r="AG45">
         <v>1.8</v>
       </c>
-      <c r="AG45">
-        <v>1.91</v>
-      </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK45">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="O46">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P46">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="Q46">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S46">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T46">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U46">
         <v>3.2</v>
       </c>
       <c r="V46">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W46">
+        <v>1.01</v>
+      </c>
+      <c r="X46">
+        <v>1.04</v>
+      </c>
+      <c r="Y46">
+        <v>1.36</v>
+      </c>
+      <c r="Z46">
+        <v>2.8</v>
+      </c>
+      <c r="AA46">
+        <v>2.15</v>
+      </c>
+      <c r="AB46">
+        <v>1.62</v>
+      </c>
+      <c r="AC46">
+        <v>4.4</v>
+      </c>
+      <c r="AD46">
+        <v>1.17</v>
+      </c>
+      <c r="AE46">
+        <v>1.02</v>
+      </c>
+      <c r="AF46">
+        <v>2.15</v>
+      </c>
+      <c r="AG46">
+        <v>1.6</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.06</v>
       </c>
-      <c r="X46">
-        <v>1.03</v>
-      </c>
-      <c r="Y46">
-        <v>1.34</v>
-      </c>
-      <c r="Z46">
-        <v>2.78</v>
-      </c>
-      <c r="AA46">
-        <v>2.13</v>
-      </c>
-      <c r="AB46">
-        <v>1.65</v>
-      </c>
-      <c r="AC46">
-        <v>4.1</v>
-      </c>
-      <c r="AD46">
-        <v>1.19</v>
-      </c>
-      <c r="AE46">
-        <v>1.03</v>
-      </c>
-      <c r="AF46">
-        <v>2.16</v>
-      </c>
-      <c r="AG46">
-        <v>1.62</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.04</v>
-      </c>
       <c r="AK46">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,31 +7970,31 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="O47">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P47">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="Q47">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S47">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T47">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="U47">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="V47">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W47">
         <v>1.04</v>
@@ -8003,22 +8003,22 @@
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z47">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA47">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AB47">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC47">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AD47">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE47">
         <v>1.06</v>
@@ -8027,7 +8027,7 @@
         <v>1.83</v>
       </c>
       <c r="AG47">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AK47">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -950,14 +950,14 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49", "90+4"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -2082,23 +2082,23 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "78", "88"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,26 +2242,26 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "87"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2344,16 +2344,16 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ12">
         <v>0</v>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2424,111 +2424,111 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P13">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="Q13">
+        <v>1.85</v>
+      </c>
+      <c r="R13">
+        <v>2.43</v>
+      </c>
+      <c r="S13">
+        <v>1.2</v>
+      </c>
+      <c r="T13">
+        <v>2.75</v>
+      </c>
+      <c r="U13">
+        <v>1.92</v>
+      </c>
+      <c r="V13">
+        <v>1.47</v>
+      </c>
+      <c r="W13">
+        <v>1.09</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>1.13</v>
+      </c>
+      <c r="Z13">
+        <v>3.13</v>
+      </c>
+      <c r="AA13">
+        <v>1.45</v>
+      </c>
+      <c r="AB13">
+        <v>2.31</v>
+      </c>
+      <c r="AC13">
         <v>2.3</v>
       </c>
-      <c r="R13">
-        <v>2.12</v>
-      </c>
-      <c r="S13">
-        <v>1.3</v>
-      </c>
-      <c r="T13">
-        <v>3.2</v>
-      </c>
-      <c r="U13">
-        <v>2.44</v>
-      </c>
-      <c r="V13">
-        <v>1.44</v>
-      </c>
-      <c r="W13">
-        <v>1.1</v>
-      </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.19</v>
-      </c>
-      <c r="Z13">
-        <v>3.75</v>
-      </c>
-      <c r="AA13">
-        <v>1.73</v>
-      </c>
-      <c r="AB13">
-        <v>1.95</v>
-      </c>
-      <c r="AC13">
-        <v>2.81</v>
-      </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE13">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>["30"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK13">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,84 +2559,84 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="O14">
+        <v>3.75</v>
+      </c>
+      <c r="P14">
         <v>3.5</v>
       </c>
-      <c r="P14">
-        <v>1.85</v>
-      </c>
       <c r="Q14">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U14">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AA14">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AC14">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AD14">
         <v>1.44</v>
@@ -2645,53 +2645,53 @@
         <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "85", "90+3"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "78"]</t>
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,139 +2722,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
         <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="AA15">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AB15">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AC15">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="AD15">
         <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "24", "75"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "89"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,19 +2885,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2909,24 +2909,24 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="O16">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>4.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q16">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="R16">
         <v>2.4</v>
@@ -2935,46 +2935,46 @@
         <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z16">
         <v>4.5</v>
       </c>
       <c r="AA16">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="AC16">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AD16">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AE16">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2983,41 +2983,41 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "65"]</t>
         </is>
       </c>
       <c r="AJ16">
         <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,19 +3048,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3072,39 +3072,39 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q17">
-        <v>3.53</v>
+        <v>2.41</v>
       </c>
       <c r="R17">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T17">
         <v>3.12</v>
       </c>
       <c r="U17">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3113,31 +3113,31 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB17">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="AC17">
-        <v>2.69</v>
+        <v>2.46</v>
       </c>
       <c r="AD17">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE17">
         <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3146,41 +3146,41 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,139 +3211,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="R18">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="T18">
-        <v>2.89</v>
+        <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W18">
+        <v>1.1</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.11</v>
+      </c>
+      <c r="Z18">
+        <v>4.9</v>
+      </c>
+      <c r="AA18">
+        <v>1.44</v>
+      </c>
+      <c r="AB18">
+        <v>2.05</v>
+      </c>
+      <c r="AC18">
+        <v>2.4</v>
+      </c>
+      <c r="AD18">
+        <v>1.65</v>
+      </c>
+      <c r="AE18">
+        <v>1.2</v>
+      </c>
+      <c r="AF18">
+        <v>1.44</v>
+      </c>
+      <c r="AG18">
+        <v>2.59</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>["38", "71", "75"]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>["42", "45", "82"]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.08</v>
       </c>
-      <c r="X18">
-        <v>1.04</v>
-      </c>
-      <c r="Y18">
-        <v>1.22</v>
-      </c>
-      <c r="Z18">
-        <v>4.2</v>
-      </c>
-      <c r="AA18">
-        <v>1.73</v>
-      </c>
-      <c r="AB18">
-        <v>1.99</v>
-      </c>
-      <c r="AC18">
-        <v>2.83</v>
-      </c>
-      <c r="AD18">
-        <v>1.4</v>
-      </c>
-      <c r="AE18">
-        <v>1.09</v>
-      </c>
-      <c r="AF18">
-        <v>1.62</v>
-      </c>
-      <c r="AG18">
-        <v>2.2</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.22</v>
-      </c>
       <c r="AK18">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,51 +3383,51 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
         <v>3.25</v>
       </c>
       <c r="P19">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q19">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
         <v>2.07</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T19">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="U19">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
         <v>1.4</v>
@@ -3436,43 +3436,43 @@
         <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
         <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB19">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC19">
         <v>3.05</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "77", "86", "90+5"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68", "71"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3561,115 +3561,115 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q20">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R20">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U20">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA20">
+        <v>1.8</v>
+      </c>
+      <c r="AB20">
+        <v>2</v>
+      </c>
+      <c r="AC20">
+        <v>2.74</v>
+      </c>
+      <c r="AD20">
+        <v>1.35</v>
+      </c>
+      <c r="AE20">
+        <v>1.11</v>
+      </c>
+      <c r="AF20">
+        <v>1.85</v>
+      </c>
+      <c r="AG20">
+        <v>1.81</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>["23"]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>["79"]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.07</v>
+      </c>
+      <c r="AK20">
+        <v>2.43</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>11</v>
+      </c>
+      <c r="AN20">
+        <v>8</v>
+      </c>
+      <c r="AO20">
+        <v>18</v>
+      </c>
+      <c r="AP20">
+        <v>12</v>
+      </c>
+      <c r="AQ20">
+        <v>2.76</v>
+      </c>
+      <c r="AR20">
         <v>1.78</v>
       </c>
-      <c r="AB20">
-        <v>1.91</v>
-      </c>
-      <c r="AC20">
-        <v>2.83</v>
-      </c>
-      <c r="AD20">
-        <v>1.33</v>
-      </c>
-      <c r="AE20">
-        <v>1.13</v>
-      </c>
-      <c r="AF20">
-        <v>1.82</v>
-      </c>
-      <c r="AG20">
-        <v>1.85</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.11</v>
-      </c>
-      <c r="AK20">
-        <v>2.2</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>-1</v>
-      </c>
-      <c r="AN20">
-        <v>-1</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>-1</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
       <c r="AS20">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -3721,51 +3721,51 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S21">
         <v>1.37</v>
       </c>
       <c r="T21">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U21">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="V21">
         <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z21">
         <v>3.1</v>
@@ -3774,10 +3774,10 @@
         <v>1.88</v>
       </c>
       <c r="AB21">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC21">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD21">
         <v>1.23</v>
@@ -3786,53 +3786,53 @@
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AG21">
         <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "90+8"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK21">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "51", "54", "57", "60", "87"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4047,14 +4047,14 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,36 +4198,36 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O24">
-        <v>8.1</v>
+        <v>7.57</v>
       </c>
       <c r="P24">
-        <v>14</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB24">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "83"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,130 +4361,130 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="O25">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="P25">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q25">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="R25">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="S25">
+        <v>1.2</v>
+      </c>
+      <c r="T25">
+        <v>4</v>
+      </c>
+      <c r="U25">
+        <v>2.1</v>
+      </c>
+      <c r="V25">
+        <v>1.65</v>
+      </c>
+      <c r="W25">
+        <v>1.2</v>
+      </c>
+      <c r="X25">
+        <v>1.01</v>
+      </c>
+      <c r="Y25">
+        <v>1.11</v>
+      </c>
+      <c r="Z25">
+        <v>5.5</v>
+      </c>
+      <c r="AA25">
+        <v>1.38</v>
+      </c>
+      <c r="AB25">
+        <v>2.62</v>
+      </c>
+      <c r="AC25">
+        <v>2.04</v>
+      </c>
+      <c r="AD25">
+        <v>1.67</v>
+      </c>
+      <c r="AE25">
         <v>1.25</v>
       </c>
-      <c r="T25">
-        <v>3.6</v>
-      </c>
-      <c r="U25">
-        <v>2.2</v>
-      </c>
-      <c r="V25">
-        <v>1.6</v>
-      </c>
-      <c r="W25">
-        <v>1.15</v>
-      </c>
-      <c r="X25">
-        <v>1.02</v>
-      </c>
-      <c r="Y25">
-        <v>1.14</v>
-      </c>
-      <c r="Z25">
-        <v>4.6</v>
-      </c>
-      <c r="AA25">
-        <v>1.46</v>
-      </c>
-      <c r="AB25">
-        <v>2.38</v>
-      </c>
-      <c r="AC25">
-        <v>2.22</v>
-      </c>
-      <c r="AD25">
-        <v>1.56</v>
-      </c>
-      <c r="AE25">
-        <v>1.19</v>
-      </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
         <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "50", "90+1", "90+5"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54", "58"]</t>
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK25">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,26 +4524,26 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4553,71 +4553,71 @@
         <v>5.7</v>
       </c>
       <c r="P26">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="Q26">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R26">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="S26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T26">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V26">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="W26">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z26">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>1.25</v>
       </c>
       <c r="AB26">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AC26">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD26">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AE26">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
+          <t>["22", "30", "40", "57", "78", "85"]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ26">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK26">
         <v>4.5</v>
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,36 +4687,36 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.73</v>
+        <v>3.45</v>
       </c>
       <c r="O27">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>2.37</v>
+        <v>1.94</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4771,14 +4771,14 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
+          <t>["45+4", "90+3"]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ27">
         <v>0</v>
       </c>
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -4862,14 +4862,14 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72", "86"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "73"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,26 +5013,26 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "87"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82", "85"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,13 +5176,13 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5191,11 +5191,11 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46", "58"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5330,139 +5330,139 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
+        <v>2.3</v>
+      </c>
+      <c r="O31">
+        <v>2.8</v>
+      </c>
+      <c r="P31">
+        <v>2.8</v>
+      </c>
+      <c r="Q31">
+        <v>2.97</v>
+      </c>
+      <c r="R31">
+        <v>2.11</v>
+      </c>
+      <c r="S31">
+        <v>1.48</v>
+      </c>
+      <c r="T31">
+        <v>2.34</v>
+      </c>
+      <c r="U31">
+        <v>3.08</v>
+      </c>
+      <c r="V31">
+        <v>1.28</v>
+      </c>
+      <c r="W31">
+        <v>1.05</v>
+      </c>
+      <c r="X31">
+        <v>1.04</v>
+      </c>
+      <c r="Y31">
+        <v>1.34</v>
+      </c>
+      <c r="Z31">
+        <v>2.78</v>
+      </c>
+      <c r="AA31">
+        <v>2.13</v>
+      </c>
+      <c r="AB31">
+        <v>1.61</v>
+      </c>
+      <c r="AC31">
+        <v>3.72</v>
+      </c>
+      <c r="AD31">
+        <v>1.2</v>
+      </c>
+      <c r="AE31">
+        <v>1.04</v>
+      </c>
+      <c r="AF31">
+        <v>1.82</v>
+      </c>
+      <c r="AG31">
+        <v>1.83</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>["67"]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>["37", "44", "59"]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.31</v>
+      </c>
+      <c r="AK31">
+        <v>1.5</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>4</v>
+      </c>
+      <c r="AN31">
+        <v>6</v>
+      </c>
+      <c r="AO31">
+        <v>13</v>
+      </c>
+      <c r="AP31">
+        <v>15</v>
+      </c>
+      <c r="AQ31">
+        <v>1.51</v>
+      </c>
+      <c r="AR31">
         <v>1.71</v>
       </c>
-      <c r="O31">
-        <v>3.7</v>
-      </c>
-      <c r="P31">
-        <v>4.7</v>
-      </c>
-      <c r="Q31">
-        <v>2.2</v>
-      </c>
-      <c r="R31">
-        <v>2.32</v>
-      </c>
-      <c r="S31">
-        <v>1.33</v>
-      </c>
-      <c r="T31">
-        <v>2.84</v>
-      </c>
-      <c r="U31">
-        <v>2.59</v>
-      </c>
-      <c r="V31">
-        <v>1.41</v>
-      </c>
-      <c r="W31">
-        <v>1.07</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>1.23</v>
-      </c>
-      <c r="Z31">
-        <v>3.6</v>
-      </c>
-      <c r="AA31">
-        <v>1.88</v>
-      </c>
-      <c r="AB31">
-        <v>1.85</v>
-      </c>
-      <c r="AC31">
-        <v>3.3</v>
-      </c>
-      <c r="AD31">
-        <v>1.3</v>
-      </c>
-      <c r="AE31">
-        <v>1.08</v>
-      </c>
-      <c r="AF31">
-        <v>1.8</v>
-      </c>
-      <c r="AG31">
-        <v>1.89</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.22</v>
-      </c>
-      <c r="AK31">
-        <v>2.05</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>-1</v>
-      </c>
-      <c r="AN31">
-        <v>-1</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>-1</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
       <c r="AS31">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5493,139 +5493,139 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="O32">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q32">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="R32">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="U32">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="V32">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="AA32">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AB32">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AD32">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
+          <t>["15", "62"]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6006,21 +6006,21 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O35">
         <v>2.9</v>
       </c>
       <c r="P35">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q35">
         <v>4.8</v>
@@ -6029,28 +6029,28 @@
         <v>1.95</v>
       </c>
       <c r="S35">
+        <v>1.49</v>
+      </c>
+      <c r="T35">
+        <v>2.17</v>
+      </c>
+      <c r="U35">
+        <v>3.6</v>
+      </c>
+      <c r="V35">
+        <v>1.21</v>
+      </c>
+      <c r="W35">
+        <v>1.02</v>
+      </c>
+      <c r="X35">
+        <v>1.1</v>
+      </c>
+      <c r="Y35">
         <v>1.57</v>
       </c>
-      <c r="T35">
-        <v>2.27</v>
-      </c>
-      <c r="U35">
-        <v>3.5</v>
-      </c>
-      <c r="V35">
-        <v>1.24</v>
-      </c>
-      <c r="W35">
-        <v>1.03</v>
-      </c>
-      <c r="X35">
-        <v>1.08</v>
-      </c>
-      <c r="Y35">
-        <v>1.5</v>
-      </c>
       <c r="Z35">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AA35">
         <v>2.62</v>
@@ -6059,19 +6059,19 @@
         <v>1.44</v>
       </c>
       <c r="AC35">
-        <v>4.95</v>
+        <v>3.75</v>
       </c>
       <c r="AD35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>2.19</v>
+        <v>2.54</v>
       </c>
       <c r="AG35">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6080,41 +6080,41 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78"]</t>
         </is>
       </c>
       <c r="AJ35">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AK35">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -6336,111 +6336,111 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P37">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="Q37">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="R37">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T37">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="U37">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="V37">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>3.08</v>
+        <v>3.61</v>
       </c>
       <c r="AA37">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="AB37">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC37">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD37">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG37">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
+          <t>["45"]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ37">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK37">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6506,34 +6506,34 @@
         <v>1.36</v>
       </c>
       <c r="O38">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P38">
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="R38">
         <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="U38">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="V38">
         <v>1.33</v>
       </c>
       <c r="W38">
+        <v>1.07</v>
+      </c>
+      <c r="X38">
         <v>1.04</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
       </c>
       <c r="Y38">
         <v>1.32</v>
@@ -6554,10 +6554,10 @@
         <v>1.19</v>
       </c>
       <c r="AE38">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF38">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG38">
         <v>1.5</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>5.9</v>
+        <v>5.45</v>
       </c>
       <c r="O40">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P40">
         <v>1.39</v>
       </c>
       <c r="Q40">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="R40">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6850,22 +6850,22 @@
         <v>3.6</v>
       </c>
       <c r="U40">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V40">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="AA40">
         <v>1.53</v>
@@ -6877,7 +6877,7 @@
         <v>2.3</v>
       </c>
       <c r="AD40">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE40">
         <v>1.22</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AK40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O41">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q41">
-        <v>3.49</v>
+        <v>3.71</v>
       </c>
       <c r="R41">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T41">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="U41">
         <v>3</v>
@@ -7019,7 +7019,7 @@
         <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
         <v>1.03</v>
@@ -7034,10 +7034,10 @@
         <v>2.02</v>
       </c>
       <c r="AB41">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC41">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="AD41">
         <v>1.22</v>
@@ -7046,10 +7046,10 @@
         <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG41">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK41">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O42">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P42">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
       </c>
       <c r="R42">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S42">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T42">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="U42">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V42">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
         <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z42">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AA42">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AB42">
         <v>1.5</v>
       </c>
       <c r="AC42">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AD42">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG42">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P43">
         <v>2.3</v>
@@ -7336,13 +7336,13 @@
         <v>1.33</v>
       </c>
       <c r="T43">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U43">
         <v>2.75</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W43">
         <v>1.1</v>
@@ -7351,31 +7351,31 @@
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA43">
         <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC43">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="AD43">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE43">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
         <v>1.36</v>
@@ -8133,61 +8133,61 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O48">
         <v>3.7</v>
       </c>
       <c r="P48">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T48">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
         <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
         <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB48">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AC48">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="AD48">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
         <v>2.3</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="R49">
         <v>2.21</v>
@@ -8317,43 +8317,43 @@
         <v>3.5</v>
       </c>
       <c r="U49">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="V49">
+        <v>1.5</v>
+      </c>
+      <c r="W49">
+        <v>1.11</v>
+      </c>
+      <c r="X49">
+        <v>1.02</v>
+      </c>
+      <c r="Y49">
+        <v>1.16</v>
+      </c>
+      <c r="Z49">
+        <v>4.05</v>
+      </c>
+      <c r="AA49">
+        <v>1.6</v>
+      </c>
+      <c r="AB49">
+        <v>2.15</v>
+      </c>
+      <c r="AC49">
+        <v>2.52</v>
+      </c>
+      <c r="AD49">
+        <v>1.44</v>
+      </c>
+      <c r="AE49">
+        <v>1.14</v>
+      </c>
+      <c r="AF49">
         <v>1.53</v>
       </c>
-      <c r="W49">
-        <v>1.13</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.17</v>
-      </c>
-      <c r="Z49">
-        <v>4.25</v>
-      </c>
-      <c r="AA49">
-        <v>1.55</v>
-      </c>
-      <c r="AB49">
-        <v>2.17</v>
-      </c>
-      <c r="AC49">
-        <v>2.63</v>
-      </c>
-      <c r="AD49">
-        <v>1.47</v>
-      </c>
-      <c r="AE49">
-        <v>1.17</v>
-      </c>
-      <c r="AF49">
-        <v>1.5</v>
-      </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,37 +8462,37 @@
         <v>1.09</v>
       </c>
       <c r="O50">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P50">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q50">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="R50">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="S50">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="T50">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="U50">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V50">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="W50">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="X50">
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z50">
         <v>15</v>
@@ -8501,22 +8501,22 @@
         <v>1.08</v>
       </c>
       <c r="AB50">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AC50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD50">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AE50">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.03</v>
       </c>
       <c r="AK50">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -6166,14 +6166,14 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65", "87"]</t>
         </is>
       </c>
       <c r="AJ36">
@@ -6256,28 +6256,28 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -6492,14 +6492,14 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "69"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
@@ -6582,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6643,26 +6643,26 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "69", "79"]</t>
         </is>
       </c>
       <c r="AJ39">
@@ -6745,16 +6745,16 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ39">
         <v>0</v>
@@ -6806,26 +6806,26 @@
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2"]</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "89"]</t>
         </is>
       </c>
       <c r="AJ40">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,16 +6969,16 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16"]</t>
         </is>
       </c>
       <c r="AJ41">
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -7144,14 +7144,14 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,69 +7477,69 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q44">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="R44">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="U44">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V44">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z44">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA44">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AB44">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC44">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD44">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE44">
         <v>1.02</v>
       </c>
       <c r="AF44">
+        <v>1.84</v>
+      </c>
+      <c r="AG44">
         <v>1.8</v>
       </c>
-      <c r="AG44">
-        <v>1.91</v>
-      </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7551,37 +7551,37 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AL44">
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7612,139 +7612,139 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="O45">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P45">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q45">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="R45">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S45">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T45">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="U45">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V45">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W45">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z45">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA45">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AB45">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC45">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD45">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE45">
         <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG45">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "24"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "66"]</t>
         </is>
       </c>
       <c r="AJ45">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK45">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,26 +7784,26 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "70"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "90+5"]</t>
         </is>
       </c>
       <c r="AJ46">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,26 +7947,26 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "78"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "33"]</t>
         </is>
       </c>
       <c r="AJ47">
@@ -8049,28 +8049,28 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8110,26 +8110,26 @@
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "45+2", "86"]</t>
         </is>
       </c>
       <c r="AJ48">
@@ -8212,28 +8212,28 @@
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8296,25 +8296,25 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O49">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
         <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="R49">
         <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
         <v>2.34</v>
@@ -8335,10 +8335,10 @@
         <v>4.05</v>
       </c>
       <c r="AA49">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB49">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC49">
         <v>2.52</v>
@@ -8353,7 +8353,7 @@
         <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8465,25 +8465,25 @@
         <v>12</v>
       </c>
       <c r="P50">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q50">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R50">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="S50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T50">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U50">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V50">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="W50">
         <v>1.34</v>
@@ -8492,31 +8492,31 @@
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z50">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA50">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB50">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AC50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD50">
         <v>2.9</v>
       </c>
       <c r="AE50">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
